--- a/artfynd/A 28725-2024 artfynd.xlsx
+++ b/artfynd/A 28725-2024 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119536328</v>
+        <v>119537029</v>
       </c>
       <c r="B7" t="n">
-        <v>79608</v>
+        <v>82305</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539505</v>
+        <v>539525</v>
       </c>
       <c r="R7" t="n">
-        <v>7203689</v>
+        <v>7203612</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536341</v>
+        <v>119536884</v>
       </c>
       <c r="B8" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539268</v>
+        <v>539427</v>
       </c>
       <c r="R8" t="n">
-        <v>7204021</v>
+        <v>7203760</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119535983</v>
+        <v>119536891</v>
       </c>
       <c r="B9" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1421,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539249</v>
+        <v>539381</v>
       </c>
       <c r="R9" t="n">
-        <v>7203985</v>
+        <v>7203929</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119537029</v>
+        <v>119536328</v>
       </c>
       <c r="B10" t="n">
-        <v>82305</v>
+        <v>79608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539525</v>
+        <v>539505</v>
       </c>
       <c r="R10" t="n">
-        <v>7203612</v>
+        <v>7203689</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536884</v>
+        <v>119536341</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539427</v>
+        <v>539268</v>
       </c>
       <c r="R11" t="n">
-        <v>7203760</v>
+        <v>7204021</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119536891</v>
+        <v>119535983</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,25 +1757,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539381</v>
+        <v>539249</v>
       </c>
       <c r="R12" t="n">
-        <v>7203929</v>
+        <v>7203985</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -4564,10 +4564,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119536903</v>
+        <v>119536346</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4580,21 +4580,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>539306</v>
+        <v>539419</v>
       </c>
       <c r="R37" t="n">
-        <v>7204148</v>
+        <v>7203720</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4676,10 +4676,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119536915</v>
+        <v>119536403</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>94323</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4688,25 +4688,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539474</v>
+        <v>539514</v>
       </c>
       <c r="R38" t="n">
-        <v>7203605</v>
+        <v>7203744</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4788,10 +4788,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119535950</v>
+        <v>119536915</v>
       </c>
       <c r="B39" t="n">
-        <v>104994</v>
+        <v>78526</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4800,25 +4800,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4828,10 +4828,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539261</v>
+        <v>539474</v>
       </c>
       <c r="R39" t="n">
-        <v>7203983</v>
+        <v>7203605</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4900,10 +4900,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119536346</v>
+        <v>119536903</v>
       </c>
       <c r="B40" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4916,21 +4916,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539419</v>
+        <v>539306</v>
       </c>
       <c r="R40" t="n">
-        <v>7203720</v>
+        <v>7204148</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5012,10 +5012,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119536403</v>
+        <v>119535950</v>
       </c>
       <c r="B41" t="n">
-        <v>94323</v>
+        <v>104994</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5028,21 +5028,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2813</v>
+        <v>221725</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5052,10 +5052,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>539514</v>
+        <v>539261</v>
       </c>
       <c r="R41" t="n">
-        <v>7203744</v>
+        <v>7203983</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5913,10 +5913,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119537129</v>
+        <v>119536344</v>
       </c>
       <c r="B49" t="n">
-        <v>79642</v>
+        <v>79608</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5925,25 +5925,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>539380</v>
+        <v>539392</v>
       </c>
       <c r="R49" t="n">
-        <v>7203902</v>
+        <v>7203749</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6025,10 +6025,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119536344</v>
+        <v>119536870</v>
       </c>
       <c r="B50" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6041,21 +6041,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6065,10 +6065,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>539392</v>
+        <v>539517</v>
       </c>
       <c r="R50" t="n">
-        <v>7203749</v>
+        <v>7203551</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6137,10 +6137,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119536870</v>
+        <v>119537129</v>
       </c>
       <c r="B51" t="n">
-        <v>78526</v>
+        <v>79642</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6149,20 +6149,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>539517</v>
+        <v>539380</v>
       </c>
       <c r="R51" t="n">
-        <v>7203551</v>
+        <v>7203902</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6814,10 +6814,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119536879</v>
+        <v>119536274</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6826,25 +6826,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6854,10 +6854,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539500</v>
+        <v>539353</v>
       </c>
       <c r="R57" t="n">
-        <v>7203672</v>
+        <v>7203981</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6926,10 +6926,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119536619</v>
+        <v>119536276</v>
       </c>
       <c r="B58" t="n">
-        <v>94311</v>
+        <v>79636</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6942,21 +6942,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>539501</v>
+        <v>539490</v>
       </c>
       <c r="R58" t="n">
-        <v>7203654</v>
+        <v>7203595</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7038,10 +7038,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119536333</v>
+        <v>119537126</v>
       </c>
       <c r="B59" t="n">
-        <v>79608</v>
+        <v>79642</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7050,25 +7050,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>539410</v>
+        <v>539504</v>
       </c>
       <c r="R59" t="n">
-        <v>7203877</v>
+        <v>7203691</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7150,10 +7150,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119536274</v>
+        <v>119536619</v>
       </c>
       <c r="B60" t="n">
-        <v>79636</v>
+        <v>94311</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7166,21 +7166,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7190,10 +7190,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>539353</v>
+        <v>539501</v>
       </c>
       <c r="R60" t="n">
-        <v>7203981</v>
+        <v>7203654</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7225,7 +7225,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7262,10 +7262,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119536276</v>
+        <v>119536333</v>
       </c>
       <c r="B61" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7274,25 +7274,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7302,10 +7302,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>539490</v>
+        <v>539410</v>
       </c>
       <c r="R61" t="n">
-        <v>7203595</v>
+        <v>7203877</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7374,10 +7374,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119537126</v>
+        <v>119536879</v>
       </c>
       <c r="B62" t="n">
-        <v>79642</v>
+        <v>78526</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7386,20 +7386,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7414,10 +7414,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>539504</v>
+        <v>539500</v>
       </c>
       <c r="R62" t="n">
-        <v>7203691</v>
+        <v>7203672</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7598,10 +7598,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119537048</v>
+        <v>119536889</v>
       </c>
       <c r="B64" t="n">
-        <v>90043</v>
+        <v>78526</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7614,21 +7614,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3286</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>539427</v>
+        <v>539408</v>
       </c>
       <c r="R64" t="n">
-        <v>7203770</v>
+        <v>7203874</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7710,7 +7710,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119536889</v>
+        <v>119536909</v>
       </c>
       <c r="B65" t="n">
         <v>78526</v>
@@ -7750,10 +7750,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>539408</v>
+        <v>539260</v>
       </c>
       <c r="R65" t="n">
-        <v>7203874</v>
+        <v>7203982</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7822,7 +7822,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119536909</v>
+        <v>119536908</v>
       </c>
       <c r="B66" t="n">
         <v>78526</v>
@@ -7862,10 +7862,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>539260</v>
+        <v>539246</v>
       </c>
       <c r="R66" t="n">
-        <v>7203982</v>
+        <v>7203987</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7934,10 +7934,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119536908</v>
+        <v>119537048</v>
       </c>
       <c r="B67" t="n">
-        <v>78526</v>
+        <v>90043</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7950,21 +7950,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>3286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>539246</v>
+        <v>539427</v>
       </c>
       <c r="R67" t="n">
-        <v>7203987</v>
+        <v>7203770</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9853,10 +9853,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119536332</v>
+        <v>119536107</v>
       </c>
       <c r="B84" t="n">
-        <v>79608</v>
+        <v>57463</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9869,34 +9869,43 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>539404</v>
+        <v>539353</v>
       </c>
       <c r="R84" t="n">
-        <v>7203853</v>
+        <v>7203941</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9928,7 +9937,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9938,7 +9947,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9965,10 +9974,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119536401</v>
+        <v>119536332</v>
       </c>
       <c r="B85" t="n">
-        <v>99161</v>
+        <v>79608</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9977,25 +9986,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10005,10 +10014,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>539522</v>
+        <v>539404</v>
       </c>
       <c r="R85" t="n">
-        <v>7203617</v>
+        <v>7203853</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10040,7 +10049,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10050,7 +10059,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10077,10 +10086,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119536880</v>
+        <v>119536401</v>
       </c>
       <c r="B86" t="n">
-        <v>78526</v>
+        <v>99161</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10089,25 +10098,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>2082</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10117,10 +10126,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>539505</v>
+        <v>539522</v>
       </c>
       <c r="R86" t="n">
-        <v>7203692</v>
+        <v>7203617</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10152,7 +10161,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10162,7 +10171,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10189,7 +10198,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119536910</v>
+        <v>119536880</v>
       </c>
       <c r="B87" t="n">
         <v>78526</v>
@@ -10229,10 +10238,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>539259</v>
+        <v>539505</v>
       </c>
       <c r="R87" t="n">
-        <v>7203973</v>
+        <v>7203692</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10264,7 +10273,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10274,7 +10283,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10301,7 +10310,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119536905</v>
+        <v>119536910</v>
       </c>
       <c r="B88" t="n">
         <v>78526</v>
@@ -10341,10 +10350,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>539319</v>
+        <v>539259</v>
       </c>
       <c r="R88" t="n">
-        <v>7204163</v>
+        <v>7203973</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10376,7 +10385,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10386,7 +10395,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10413,7 +10422,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119536878</v>
+        <v>119536905</v>
       </c>
       <c r="B89" t="n">
         <v>78526</v>
@@ -10453,10 +10462,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>539504</v>
+        <v>539319</v>
       </c>
       <c r="R89" t="n">
-        <v>7203658</v>
+        <v>7204163</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10488,7 +10497,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10498,7 +10507,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10525,10 +10534,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119536107</v>
+        <v>119536878</v>
       </c>
       <c r="B90" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10541,43 +10550,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>539353</v>
+        <v>539504</v>
       </c>
       <c r="R90" t="n">
-        <v>7203941</v>
+        <v>7203658</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10982,10 +10982,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119536273</v>
+        <v>119536898</v>
       </c>
       <c r="B94" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10994,25 +10994,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11022,10 +11022,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>539392</v>
+        <v>539330</v>
       </c>
       <c r="R94" t="n">
-        <v>7203821</v>
+        <v>7204056</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11057,7 +11057,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11094,7 +11094,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119536898</v>
+        <v>119536881</v>
       </c>
       <c r="B95" t="n">
         <v>78526</v>
@@ -11134,10 +11134,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>539330</v>
+        <v>539513</v>
       </c>
       <c r="R95" t="n">
-        <v>7204056</v>
+        <v>7203718</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11206,10 +11206,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119536881</v>
+        <v>119536273</v>
       </c>
       <c r="B96" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11218,25 +11218,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>539513</v>
+        <v>539392</v>
       </c>
       <c r="R96" t="n">
-        <v>7203718</v>
+        <v>7203821</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11281,7 +11281,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11766,10 +11766,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119536890</v>
+        <v>119536343</v>
       </c>
       <c r="B101" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11782,21 +11782,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11806,10 +11806,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>539381</v>
+        <v>539360</v>
       </c>
       <c r="R101" t="n">
-        <v>7203909</v>
+        <v>7203797</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11878,7 +11878,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119536343</v>
+        <v>119536342</v>
       </c>
       <c r="B102" t="n">
         <v>79608</v>
@@ -11918,10 +11918,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>539360</v>
+        <v>539259</v>
       </c>
       <c r="R102" t="n">
-        <v>7203797</v>
+        <v>7203973</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11953,7 +11953,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11990,10 +11990,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119536342</v>
+        <v>119536890</v>
       </c>
       <c r="B103" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12006,21 +12006,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12030,10 +12030,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>539259</v>
+        <v>539381</v>
       </c>
       <c r="R103" t="n">
-        <v>7203973</v>
+        <v>7203909</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12998,10 +12998,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119536875</v>
+        <v>119536347</v>
       </c>
       <c r="B112" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13014,21 +13014,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13038,10 +13038,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>539503</v>
+        <v>539474</v>
       </c>
       <c r="R112" t="n">
-        <v>7203619</v>
+        <v>7203607</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -13073,7 +13073,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13110,10 +13110,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119536913</v>
+        <v>119536330</v>
       </c>
       <c r="B113" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13126,21 +13126,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13150,10 +13150,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>539418</v>
+        <v>539440</v>
       </c>
       <c r="R113" t="n">
-        <v>7203718</v>
+        <v>7203741</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13195,7 +13195,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13446,10 +13446,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119536406</v>
+        <v>119537142</v>
       </c>
       <c r="B116" t="n">
-        <v>79511</v>
+        <v>74630</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13458,25 +13458,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6456</v>
+        <v>308</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13486,10 +13486,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>539285</v>
+        <v>539514</v>
       </c>
       <c r="R116" t="n">
-        <v>7203971</v>
+        <v>7203719</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13521,7 +13521,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13558,10 +13558,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119537142</v>
+        <v>119536875</v>
       </c>
       <c r="B117" t="n">
-        <v>74630</v>
+        <v>78526</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13574,21 +13574,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13598,10 +13598,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>539514</v>
+        <v>539503</v>
       </c>
       <c r="R117" t="n">
-        <v>7203719</v>
+        <v>7203619</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13643,7 +13643,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13670,10 +13670,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119536347</v>
+        <v>119536913</v>
       </c>
       <c r="B118" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13686,21 +13686,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>539474</v>
+        <v>539418</v>
       </c>
       <c r="R118" t="n">
-        <v>7203607</v>
+        <v>7203718</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13782,10 +13782,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119536330</v>
+        <v>119536406</v>
       </c>
       <c r="B119" t="n">
-        <v>79608</v>
+        <v>79511</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13794,25 +13794,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13822,10 +13822,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>539440</v>
+        <v>539285</v>
       </c>
       <c r="R119" t="n">
-        <v>7203741</v>
+        <v>7203971</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13857,7 +13857,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13867,7 +13867,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD119" t="b">

--- a/artfynd/A 28725-2024 artfynd.xlsx
+++ b/artfynd/A 28725-2024 artfynd.xlsx
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119536902</v>
+        <v>119535949</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>104994</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1981,25 +1981,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539340</v>
+        <v>539400</v>
       </c>
       <c r="R14" t="n">
-        <v>7204108</v>
+        <v>7203837</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119536883</v>
+        <v>119535962</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>77473</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539438</v>
+        <v>539520</v>
       </c>
       <c r="R15" t="n">
-        <v>7203740</v>
+        <v>7203618</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119537248</v>
+        <v>119536007</v>
       </c>
       <c r="B16" t="n">
-        <v>77910</v>
+        <v>90562</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2209,21 +2209,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>539311</v>
+        <v>539248</v>
       </c>
       <c r="R16" t="n">
-        <v>7203961</v>
+        <v>7203984</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119536900</v>
+        <v>119536331</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2321,21 +2321,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>539326</v>
+        <v>539389</v>
       </c>
       <c r="R17" t="n">
-        <v>7204101</v>
+        <v>7203819</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119536331</v>
+        <v>119536902</v>
       </c>
       <c r="B18" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2433,21 +2433,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>539389</v>
+        <v>539340</v>
       </c>
       <c r="R18" t="n">
-        <v>7203819</v>
+        <v>7204108</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2529,10 +2529,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119535949</v>
+        <v>119536883</v>
       </c>
       <c r="B19" t="n">
-        <v>104994</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2541,25 +2541,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>539400</v>
+        <v>539438</v>
       </c>
       <c r="R19" t="n">
-        <v>7203837</v>
+        <v>7203740</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2641,10 +2641,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119535962</v>
+        <v>119537248</v>
       </c>
       <c r="B20" t="n">
-        <v>77473</v>
+        <v>77910</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2657,21 +2657,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>314</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>539520</v>
+        <v>539311</v>
       </c>
       <c r="R20" t="n">
-        <v>7203618</v>
+        <v>7203961</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2753,10 +2753,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119536007</v>
+        <v>119536900</v>
       </c>
       <c r="B21" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2769,21 +2769,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>539248</v>
+        <v>539326</v>
       </c>
       <c r="R21" t="n">
-        <v>7203984</v>
+        <v>7204101</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -7598,10 +7598,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119536889</v>
+        <v>119537048</v>
       </c>
       <c r="B64" t="n">
-        <v>78526</v>
+        <v>90043</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7614,21 +7614,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>3286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>539408</v>
+        <v>539427</v>
       </c>
       <c r="R64" t="n">
-        <v>7203874</v>
+        <v>7203770</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7710,7 +7710,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119536909</v>
+        <v>119536889</v>
       </c>
       <c r="B65" t="n">
         <v>78526</v>
@@ -7750,10 +7750,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>539260</v>
+        <v>539408</v>
       </c>
       <c r="R65" t="n">
-        <v>7203982</v>
+        <v>7203874</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7822,7 +7822,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119536908</v>
+        <v>119536909</v>
       </c>
       <c r="B66" t="n">
         <v>78526</v>
@@ -7862,10 +7862,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>539246</v>
+        <v>539260</v>
       </c>
       <c r="R66" t="n">
-        <v>7203987</v>
+        <v>7203982</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7934,10 +7934,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119537048</v>
+        <v>119536908</v>
       </c>
       <c r="B67" t="n">
-        <v>90043</v>
+        <v>78526</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7950,21 +7950,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3286</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>539427</v>
+        <v>539246</v>
       </c>
       <c r="R67" t="n">
-        <v>7203770</v>
+        <v>7203987</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8382,10 +8382,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119537112</v>
+        <v>119536882</v>
       </c>
       <c r="B71" t="n">
-        <v>91128</v>
+        <v>78526</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8394,25 +8394,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>539486</v>
+        <v>539508</v>
       </c>
       <c r="R71" t="n">
-        <v>7203594</v>
+        <v>7203755</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8457,7 +8457,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8494,10 +8494,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119536493</v>
+        <v>119536912</v>
       </c>
       <c r="B72" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8510,21 +8510,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8534,10 +8534,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>539429</v>
+        <v>539412</v>
       </c>
       <c r="R72" t="n">
-        <v>7203761</v>
+        <v>7203743</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8606,10 +8606,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119536005</v>
+        <v>119536904</v>
       </c>
       <c r="B73" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8622,21 +8622,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8646,10 +8646,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>539315</v>
+        <v>539309</v>
       </c>
       <c r="R73" t="n">
-        <v>7204159</v>
+        <v>7204157</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8718,7 +8718,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119536882</v>
+        <v>119536888</v>
       </c>
       <c r="B74" t="n">
         <v>78526</v>
@@ -8758,10 +8758,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>539508</v>
+        <v>539404</v>
       </c>
       <c r="R74" t="n">
-        <v>7203755</v>
+        <v>7203854</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8830,10 +8830,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119536912</v>
+        <v>119537245</v>
       </c>
       <c r="B75" t="n">
-        <v>78526</v>
+        <v>90957</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8842,25 +8842,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8870,10 +8870,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>539412</v>
+        <v>539319</v>
       </c>
       <c r="R75" t="n">
-        <v>7203743</v>
+        <v>7204161</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8942,10 +8942,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119536904</v>
+        <v>119536681</v>
       </c>
       <c r="B76" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8954,25 +8954,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8982,10 +8982,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>539309</v>
+        <v>539381</v>
       </c>
       <c r="R76" t="n">
-        <v>7204157</v>
+        <v>7203902</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9054,10 +9054,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119536888</v>
+        <v>119536405</v>
       </c>
       <c r="B77" t="n">
-        <v>78526</v>
+        <v>79511</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9066,25 +9066,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9094,10 +9094,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>539404</v>
+        <v>539273</v>
       </c>
       <c r="R77" t="n">
-        <v>7203854</v>
+        <v>7203974</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9166,10 +9166,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119537245</v>
+        <v>119536024</v>
       </c>
       <c r="B78" t="n">
-        <v>90957</v>
+        <v>57310</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9178,38 +9178,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>539319</v>
+        <v>539515</v>
       </c>
       <c r="R78" t="n">
-        <v>7204161</v>
+        <v>7203720</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9241,7 +9246,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9251,7 +9256,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9278,10 +9283,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119536681</v>
+        <v>119536025</v>
       </c>
       <c r="B79" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9290,38 +9295,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>539381</v>
+        <v>539346</v>
       </c>
       <c r="R79" t="n">
-        <v>7203902</v>
+        <v>7203957</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9353,7 +9363,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9363,7 +9373,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9390,10 +9400,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119536405</v>
+        <v>119536027</v>
       </c>
       <c r="B80" t="n">
-        <v>79511</v>
+        <v>57310</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9402,38 +9412,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>539273</v>
+        <v>539326</v>
       </c>
       <c r="R80" t="n">
-        <v>7203974</v>
+        <v>7204100</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9465,7 +9480,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9475,7 +9490,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9502,10 +9517,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119536024</v>
+        <v>119537112</v>
       </c>
       <c r="B81" t="n">
-        <v>57310</v>
+        <v>91128</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9514,43 +9529,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>539515</v>
+        <v>539486</v>
       </c>
       <c r="R81" t="n">
-        <v>7203720</v>
+        <v>7203594</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9582,7 +9592,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9592,7 +9602,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9619,10 +9629,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119536025</v>
+        <v>119536493</v>
       </c>
       <c r="B82" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9635,39 +9645,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>539346</v>
+        <v>539429</v>
       </c>
       <c r="R82" t="n">
-        <v>7203957</v>
+        <v>7203761</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9699,7 +9704,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9709,7 +9714,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9736,10 +9741,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119536027</v>
+        <v>119536005</v>
       </c>
       <c r="B83" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9752,39 +9757,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>539326</v>
+        <v>539315</v>
       </c>
       <c r="R83" t="n">
-        <v>7204100</v>
+        <v>7204159</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9853,10 +9853,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119536107</v>
+        <v>119536332</v>
       </c>
       <c r="B84" t="n">
-        <v>57463</v>
+        <v>79608</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9869,43 +9869,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>539353</v>
+        <v>539404</v>
       </c>
       <c r="R84" t="n">
-        <v>7203941</v>
+        <v>7203853</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9937,7 +9928,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9947,7 +9938,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9974,10 +9965,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119536332</v>
+        <v>119536401</v>
       </c>
       <c r="B85" t="n">
-        <v>79608</v>
+        <v>99161</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9986,25 +9977,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10014,10 +10005,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>539404</v>
+        <v>539522</v>
       </c>
       <c r="R85" t="n">
-        <v>7203853</v>
+        <v>7203617</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10049,7 +10040,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10059,7 +10050,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10086,10 +10077,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119536401</v>
+        <v>119536880</v>
       </c>
       <c r="B86" t="n">
-        <v>99161</v>
+        <v>78526</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10098,25 +10089,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2082</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10126,10 +10117,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>539522</v>
+        <v>539505</v>
       </c>
       <c r="R86" t="n">
-        <v>7203617</v>
+        <v>7203692</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10161,7 +10152,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10171,7 +10162,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10198,7 +10189,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119536880</v>
+        <v>119536910</v>
       </c>
       <c r="B87" t="n">
         <v>78526</v>
@@ -10238,10 +10229,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>539505</v>
+        <v>539259</v>
       </c>
       <c r="R87" t="n">
-        <v>7203692</v>
+        <v>7203973</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10273,7 +10264,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10283,7 +10274,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10310,7 +10301,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119536910</v>
+        <v>119536905</v>
       </c>
       <c r="B88" t="n">
         <v>78526</v>
@@ -10350,10 +10341,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>539259</v>
+        <v>539319</v>
       </c>
       <c r="R88" t="n">
-        <v>7203973</v>
+        <v>7204163</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10385,7 +10376,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10395,7 +10386,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10422,7 +10413,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119536905</v>
+        <v>119536878</v>
       </c>
       <c r="B89" t="n">
         <v>78526</v>
@@ -10462,10 +10453,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>539319</v>
+        <v>539504</v>
       </c>
       <c r="R89" t="n">
-        <v>7204163</v>
+        <v>7203658</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10497,7 +10488,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10507,7 +10498,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10534,10 +10525,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119536878</v>
+        <v>119536107</v>
       </c>
       <c r="B90" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10550,34 +10541,43 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>539504</v>
+        <v>539353</v>
       </c>
       <c r="R90" t="n">
-        <v>7203658</v>
+        <v>7203941</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10982,10 +10982,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119536898</v>
+        <v>119536273</v>
       </c>
       <c r="B94" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10994,25 +10994,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11022,10 +11022,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>539330</v>
+        <v>539392</v>
       </c>
       <c r="R94" t="n">
-        <v>7204056</v>
+        <v>7203821</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11057,7 +11057,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11094,7 +11094,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119536881</v>
+        <v>119536898</v>
       </c>
       <c r="B95" t="n">
         <v>78526</v>
@@ -11134,10 +11134,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>539513</v>
+        <v>539330</v>
       </c>
       <c r="R95" t="n">
-        <v>7203718</v>
+        <v>7204056</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11206,10 +11206,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119536273</v>
+        <v>119536881</v>
       </c>
       <c r="B96" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11218,25 +11218,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>539392</v>
+        <v>539513</v>
       </c>
       <c r="R96" t="n">
-        <v>7203821</v>
+        <v>7203718</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11281,7 +11281,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12998,10 +12998,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119536347</v>
+        <v>119536875</v>
       </c>
       <c r="B112" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13014,21 +13014,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13038,10 +13038,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>539474</v>
+        <v>539503</v>
       </c>
       <c r="R112" t="n">
-        <v>7203607</v>
+        <v>7203619</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -13073,7 +13073,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13110,10 +13110,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119536330</v>
+        <v>119536913</v>
       </c>
       <c r="B113" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13126,21 +13126,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13150,10 +13150,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>539440</v>
+        <v>539418</v>
       </c>
       <c r="R113" t="n">
-        <v>7203741</v>
+        <v>7203718</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13195,7 +13195,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13446,10 +13446,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119537142</v>
+        <v>119536406</v>
       </c>
       <c r="B116" t="n">
-        <v>74630</v>
+        <v>79511</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13458,25 +13458,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>308</v>
+        <v>6456</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13486,10 +13486,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>539514</v>
+        <v>539285</v>
       </c>
       <c r="R116" t="n">
-        <v>7203719</v>
+        <v>7203971</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13521,7 +13521,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13558,10 +13558,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119536875</v>
+        <v>119537142</v>
       </c>
       <c r="B117" t="n">
-        <v>78526</v>
+        <v>74630</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13574,21 +13574,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13598,10 +13598,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>539503</v>
+        <v>539514</v>
       </c>
       <c r="R117" t="n">
-        <v>7203619</v>
+        <v>7203719</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13643,7 +13643,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13670,10 +13670,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119536913</v>
+        <v>119536347</v>
       </c>
       <c r="B118" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13686,21 +13686,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>539418</v>
+        <v>539474</v>
       </c>
       <c r="R118" t="n">
-        <v>7203718</v>
+        <v>7203607</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13782,10 +13782,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119536406</v>
+        <v>119536330</v>
       </c>
       <c r="B119" t="n">
-        <v>79511</v>
+        <v>79608</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13794,25 +13794,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13822,10 +13822,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>539285</v>
+        <v>539440</v>
       </c>
       <c r="R119" t="n">
-        <v>7203971</v>
+        <v>7203741</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13857,7 +13857,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13867,7 +13867,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14566,10 +14566,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119536096</v>
+        <v>119536712</v>
       </c>
       <c r="B126" t="n">
-        <v>56522</v>
+        <v>90954</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14578,42 +14578,36 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>539506</v>
+        <v>539391</v>
       </c>
       <c r="R126" t="n">
-        <v>7203636</v>
+        <v>7203790</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14645,7 +14639,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14655,7 +14649,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14664,6 +14658,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -14682,10 +14677,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119536097</v>
+        <v>119536784</v>
       </c>
       <c r="B127" t="n">
-        <v>56522</v>
+        <v>97806</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14698,50 +14693,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100138</v>
+        <v>219795</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>539309</v>
+        <v>539347</v>
       </c>
       <c r="R127" t="n">
-        <v>7204157</v>
+        <v>7203938</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14773,7 +14752,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14783,7 +14762,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14810,10 +14789,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119536712</v>
+        <v>119536483</v>
       </c>
       <c r="B128" t="n">
-        <v>90954</v>
+        <v>91005</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14822,36 +14801,38 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6040186</v>
+        <v>1209</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>539391</v>
+        <v>539427</v>
       </c>
       <c r="R128" t="n">
-        <v>7203790</v>
+        <v>7203755</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14883,7 +14864,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14893,7 +14874,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14902,7 +14883,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -14921,10 +14901,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119536784</v>
+        <v>119536096</v>
       </c>
       <c r="B129" t="n">
-        <v>97806</v>
+        <v>56522</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14937,34 +14917,38 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219795</v>
+        <v>100138</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>539347</v>
+        <v>539506</v>
       </c>
       <c r="R129" t="n">
-        <v>7203938</v>
+        <v>7203636</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14996,7 +14980,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15006,7 +14990,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15033,10 +15017,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119536483</v>
+        <v>119536097</v>
       </c>
       <c r="B130" t="n">
-        <v>91005</v>
+        <v>56522</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15045,38 +15029,54 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>539427</v>
+        <v>539309</v>
       </c>
       <c r="R130" t="n">
-        <v>7203755</v>
+        <v>7204157</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -15108,7 +15108,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15118,7 +15118,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD130" t="b">

--- a/artfynd/A 28725-2024 artfynd.xlsx
+++ b/artfynd/A 28725-2024 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119537029</v>
+        <v>119535962</v>
       </c>
       <c r="B7" t="n">
-        <v>82305</v>
+        <v>77473</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539525</v>
+        <v>539520</v>
       </c>
       <c r="R7" t="n">
-        <v>7203612</v>
+        <v>7203618</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119536891</v>
+        <v>119536337</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539381</v>
+        <v>539338</v>
       </c>
       <c r="R9" t="n">
-        <v>7203929</v>
+        <v>7203941</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536328</v>
+        <v>119536345</v>
       </c>
       <c r="B10" t="n">
         <v>79608</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539505</v>
+        <v>539411</v>
       </c>
       <c r="R10" t="n">
-        <v>7203689</v>
+        <v>7203742</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536341</v>
+        <v>119536485</v>
       </c>
       <c r="B11" t="n">
-        <v>79608</v>
+        <v>91005</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,25 +1645,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539268</v>
+        <v>539324</v>
       </c>
       <c r="R11" t="n">
-        <v>7204021</v>
+        <v>7204103</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119535983</v>
+        <v>119536882</v>
       </c>
       <c r="B12" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,25 +1757,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539249</v>
+        <v>539508</v>
       </c>
       <c r="R12" t="n">
-        <v>7203985</v>
+        <v>7203755</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119536520</v>
+        <v>119536712</v>
       </c>
       <c r="B13" t="n">
-        <v>96862</v>
+        <v>90954</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1869,38 +1869,36 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539260</v>
+        <v>539391</v>
       </c>
       <c r="R13" t="n">
-        <v>7203982</v>
+        <v>7203790</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1932,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1940,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1951,6 +1949,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1969,10 +1968,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119535949</v>
+        <v>119536896</v>
       </c>
       <c r="B14" t="n">
-        <v>104994</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1981,25 +1980,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539400</v>
+        <v>539337</v>
       </c>
       <c r="R14" t="n">
-        <v>7203837</v>
+        <v>7203986</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2044,7 +2043,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2053,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119535962</v>
+        <v>119536682</v>
       </c>
       <c r="B15" t="n">
-        <v>77473</v>
+        <v>79643</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,25 +2092,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>314</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539520</v>
+        <v>539270</v>
       </c>
       <c r="R15" t="n">
-        <v>7203618</v>
+        <v>7204025</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2156,7 +2155,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2165,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2192,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119536007</v>
+        <v>119537127</v>
       </c>
       <c r="B16" t="n">
-        <v>90562</v>
+        <v>79642</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2205,25 +2204,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2233,10 +2232,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>539248</v>
+        <v>539441</v>
       </c>
       <c r="R16" t="n">
-        <v>7203984</v>
+        <v>7203738</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2268,7 +2267,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2278,7 +2277,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,7 +2304,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119536331</v>
+        <v>119536342</v>
       </c>
       <c r="B17" t="n">
         <v>79608</v>
@@ -2345,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>539389</v>
+        <v>539259</v>
       </c>
       <c r="R17" t="n">
-        <v>7203819</v>
+        <v>7203973</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2380,7 +2379,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,7 +2389,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,10 +2416,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119536902</v>
+        <v>119536554</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>90916</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2429,25 +2428,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2457,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>539340</v>
+        <v>539431</v>
       </c>
       <c r="R18" t="n">
-        <v>7204108</v>
+        <v>7203761</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2492,7 +2491,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2502,7 +2501,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2529,10 +2528,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119536883</v>
+        <v>119536718</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>79567</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2541,25 +2540,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2569,10 +2568,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>539438</v>
+        <v>539353</v>
       </c>
       <c r="R19" t="n">
-        <v>7203740</v>
+        <v>7203941</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2604,7 +2603,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2614,7 +2613,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2641,10 +2640,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119537248</v>
+        <v>119536784</v>
       </c>
       <c r="B20" t="n">
-        <v>77910</v>
+        <v>97806</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2653,25 +2652,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>219795</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2681,10 +2680,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>539311</v>
+        <v>539347</v>
       </c>
       <c r="R20" t="n">
-        <v>7203961</v>
+        <v>7203938</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2716,7 +2715,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2726,7 +2725,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2753,10 +2752,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119536900</v>
+        <v>119536790</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2769,21 +2768,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2793,10 +2792,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>539326</v>
+        <v>539492</v>
       </c>
       <c r="R21" t="n">
-        <v>7204101</v>
+        <v>7203590</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2828,7 +2827,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2838,7 +2837,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2865,10 +2864,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536338</v>
+        <v>119535983</v>
       </c>
       <c r="B22" t="n">
-        <v>79608</v>
+        <v>90527</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2877,25 +2876,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2905,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>539333</v>
+        <v>539249</v>
       </c>
       <c r="R22" t="n">
-        <v>7204016</v>
+        <v>7203985</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2940,7 +2939,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2950,7 +2949,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2977,10 +2976,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119536892</v>
+        <v>119536777</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>74622</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2989,25 +2988,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3017,10 +3016,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>539346</v>
+        <v>539510</v>
       </c>
       <c r="R23" t="n">
-        <v>7203934</v>
+        <v>7203622</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3052,7 +3051,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3062,7 +3061,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3089,10 +3088,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119536886</v>
+        <v>119535969</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3105,21 +3104,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3129,10 +3128,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>539387</v>
+        <v>539512</v>
       </c>
       <c r="R24" t="n">
-        <v>7203818</v>
+        <v>7203549</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3164,7 +3163,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3174,7 +3173,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3201,10 +3200,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119536873</v>
+        <v>119537149</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>77458</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3217,21 +3216,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3241,10 +3240,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>539528</v>
+        <v>539312</v>
       </c>
       <c r="R25" t="n">
-        <v>7203612</v>
+        <v>7203957</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3276,7 +3275,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3286,7 +3285,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3313,10 +3312,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119536685</v>
+        <v>119537128</v>
       </c>
       <c r="B26" t="n">
-        <v>79643</v>
+        <v>79642</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3329,21 +3328,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3353,10 +3352,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>539419</v>
+        <v>539389</v>
       </c>
       <c r="R26" t="n">
-        <v>7203720</v>
+        <v>7203822</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3388,7 +3387,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3398,7 +3397,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3425,10 +3424,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119536021</v>
+        <v>119536273</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>79636</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3437,43 +3436,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>539499</v>
+        <v>539392</v>
       </c>
       <c r="R27" t="n">
-        <v>7203671</v>
+        <v>7203821</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3505,7 +3499,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3515,7 +3509,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3542,10 +3536,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119536806</v>
+        <v>119536619</v>
       </c>
       <c r="B28" t="n">
-        <v>90580</v>
+        <v>94311</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3554,25 +3548,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3582,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>539337</v>
+        <v>539501</v>
       </c>
       <c r="R28" t="n">
-        <v>7204110</v>
+        <v>7203654</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3617,7 +3611,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3627,7 +3621,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3654,10 +3648,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119536020</v>
+        <v>119536339</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3670,39 +3664,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>539508</v>
+        <v>539330</v>
       </c>
       <c r="R29" t="n">
-        <v>7203619</v>
+        <v>7204058</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3734,7 +3723,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3744,7 +3733,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3771,10 +3760,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119536764</v>
+        <v>119536327</v>
       </c>
       <c r="B30" t="n">
-        <v>90558</v>
+        <v>79608</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3787,21 +3776,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3811,10 +3800,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>539508</v>
+        <v>539506</v>
       </c>
       <c r="R30" t="n">
-        <v>7203557</v>
+        <v>7203636</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3846,7 +3835,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3856,7 +3845,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3883,10 +3872,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119536872</v>
+        <v>119536005</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3899,21 +3888,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3923,10 +3912,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>539509</v>
+        <v>539315</v>
       </c>
       <c r="R31" t="n">
-        <v>7203558</v>
+        <v>7204159</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3958,7 +3947,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3968,7 +3957,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3995,10 +3984,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119536887</v>
+        <v>119536028</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4011,34 +4000,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>539398</v>
+        <v>539414</v>
       </c>
       <c r="R32" t="n">
-        <v>7203841</v>
+        <v>7203683</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4070,7 +4064,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4080,7 +4074,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4107,10 +4101,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119536911</v>
+        <v>119536328</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4123,21 +4117,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4147,10 +4141,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>539314</v>
+        <v>539505</v>
       </c>
       <c r="R33" t="n">
-        <v>7203905</v>
+        <v>7203689</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4182,7 +4176,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4192,7 +4186,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4219,7 +4213,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119536901</v>
+        <v>119536871</v>
       </c>
       <c r="B34" t="n">
         <v>78526</v>
@@ -4259,10 +4253,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>539322</v>
+        <v>539512</v>
       </c>
       <c r="R34" t="n">
-        <v>7204109</v>
+        <v>7203548</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4294,7 +4288,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4304,7 +4298,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4331,7 +4325,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536874</v>
+        <v>119536893</v>
       </c>
       <c r="B35" t="n">
         <v>78526</v>
@@ -4371,10 +4365,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>539525</v>
+        <v>539338</v>
       </c>
       <c r="R35" t="n">
-        <v>7203611</v>
+        <v>7203941</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4406,7 +4400,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4416,7 +4410,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4443,10 +4437,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536707</v>
+        <v>119536348</v>
       </c>
       <c r="B36" t="n">
-        <v>57421</v>
+        <v>79608</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4455,47 +4449,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>539474</v>
+        <v>539466</v>
       </c>
       <c r="R36" t="n">
-        <v>7203674</v>
+        <v>7203618</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4527,7 +4512,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4537,7 +4522,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4564,7 +4549,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119536346</v>
+        <v>119536332</v>
       </c>
       <c r="B37" t="n">
         <v>79608</v>
@@ -4604,10 +4589,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>539419</v>
+        <v>539404</v>
       </c>
       <c r="R37" t="n">
-        <v>7203720</v>
+        <v>7203853</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4639,7 +4624,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4649,7 +4634,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4676,10 +4661,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119536403</v>
+        <v>119536330</v>
       </c>
       <c r="B38" t="n">
-        <v>94323</v>
+        <v>79608</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4688,25 +4673,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2813</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4716,10 +4701,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539514</v>
+        <v>539440</v>
       </c>
       <c r="R38" t="n">
-        <v>7203744</v>
+        <v>7203741</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4751,7 +4736,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4761,7 +4746,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4788,10 +4773,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119536915</v>
+        <v>119536003</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4804,21 +4789,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4828,10 +4813,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539474</v>
+        <v>539322</v>
       </c>
       <c r="R39" t="n">
-        <v>7203605</v>
+        <v>7204109</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4863,7 +4848,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4873,7 +4858,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4900,10 +4885,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119536903</v>
+        <v>119536096</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>56522</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4912,38 +4897,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539306</v>
+        <v>539506</v>
       </c>
       <c r="R40" t="n">
-        <v>7204148</v>
+        <v>7203636</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4975,7 +4964,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4985,7 +4974,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5012,10 +5001,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119535950</v>
+        <v>119537029</v>
       </c>
       <c r="B41" t="n">
-        <v>104994</v>
+        <v>82305</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5024,25 +5013,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221725</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5052,10 +5041,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>539261</v>
+        <v>539525</v>
       </c>
       <c r="R41" t="n">
-        <v>7203983</v>
+        <v>7203612</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5087,7 +5076,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5097,7 +5086,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5124,10 +5113,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119536026</v>
+        <v>119536683</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>79643</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5136,43 +5125,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>539337</v>
+        <v>539259</v>
       </c>
       <c r="R42" t="n">
-        <v>7203986</v>
+        <v>7203973</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5204,7 +5188,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5214,7 +5198,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5241,10 +5225,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119536805</v>
+        <v>119536405</v>
       </c>
       <c r="B43" t="n">
-        <v>90580</v>
+        <v>79511</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5253,25 +5237,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5281,10 +5265,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>539529</v>
+        <v>539273</v>
       </c>
       <c r="R43" t="n">
-        <v>7203613</v>
+        <v>7203974</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5316,7 +5300,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5326,7 +5310,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5353,10 +5337,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119536718</v>
+        <v>119536645</v>
       </c>
       <c r="B44" t="n">
-        <v>79567</v>
+        <v>79607</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5365,25 +5349,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5393,10 +5377,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>539353</v>
+        <v>539289</v>
       </c>
       <c r="R44" t="n">
-        <v>7203941</v>
+        <v>7204141</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5428,7 +5412,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5438,7 +5422,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5465,10 +5449,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119536003</v>
+        <v>119536343</v>
       </c>
       <c r="B45" t="n">
-        <v>90562</v>
+        <v>79608</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5481,21 +5465,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5505,10 +5489,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>539322</v>
+        <v>539360</v>
       </c>
       <c r="R45" t="n">
-        <v>7204109</v>
+        <v>7203797</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5540,7 +5524,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5550,7 +5534,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5577,10 +5561,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119536485</v>
+        <v>119536403</v>
       </c>
       <c r="B46" t="n">
-        <v>91005</v>
+        <v>94323</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5589,25 +5573,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>2813</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5617,10 +5601,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>539324</v>
+        <v>539514</v>
       </c>
       <c r="R46" t="n">
-        <v>7204103</v>
+        <v>7203744</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5652,7 +5636,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5662,7 +5646,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5689,10 +5673,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119537131</v>
+        <v>119536681</v>
       </c>
       <c r="B47" t="n">
-        <v>79642</v>
+        <v>79643</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5705,21 +5689,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5729,10 +5713,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>539417</v>
+        <v>539381</v>
       </c>
       <c r="R47" t="n">
-        <v>7203723</v>
+        <v>7203902</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5764,7 +5748,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5774,7 +5758,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5801,7 +5785,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119536871</v>
+        <v>119536901</v>
       </c>
       <c r="B48" t="n">
         <v>78526</v>
@@ -5841,10 +5825,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>539512</v>
+        <v>539322</v>
       </c>
       <c r="R48" t="n">
-        <v>7203548</v>
+        <v>7204109</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5876,7 +5860,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5886,7 +5870,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5913,7 +5897,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119536344</v>
+        <v>119536347</v>
       </c>
       <c r="B49" t="n">
         <v>79608</v>
@@ -5953,10 +5937,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>539392</v>
+        <v>539474</v>
       </c>
       <c r="R49" t="n">
-        <v>7203749</v>
+        <v>7203607</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5988,7 +5972,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5998,7 +5982,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6025,10 +6009,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119536870</v>
+        <v>119536335</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6041,21 +6025,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6065,10 +6049,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>539517</v>
+        <v>539371</v>
       </c>
       <c r="R50" t="n">
-        <v>7203551</v>
+        <v>7203932</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6100,7 +6084,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6110,7 +6094,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6137,10 +6121,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119537129</v>
+        <v>119536329</v>
       </c>
       <c r="B51" t="n">
-        <v>79642</v>
+        <v>79608</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6149,25 +6133,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6177,10 +6161,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>539380</v>
+        <v>539508</v>
       </c>
       <c r="R51" t="n">
-        <v>7203902</v>
+        <v>7203755</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6212,7 +6196,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6222,7 +6206,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6249,10 +6233,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119536348</v>
+        <v>119536401</v>
       </c>
       <c r="B52" t="n">
-        <v>79608</v>
+        <v>99161</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6261,25 +6245,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6289,10 +6273,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>539466</v>
+        <v>539522</v>
       </c>
       <c r="R52" t="n">
-        <v>7203618</v>
+        <v>7203617</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6324,7 +6308,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6334,7 +6318,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6361,10 +6345,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119536345</v>
+        <v>119536274</v>
       </c>
       <c r="B53" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6373,25 +6357,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6401,10 +6385,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>539411</v>
+        <v>539353</v>
       </c>
       <c r="R53" t="n">
-        <v>7203742</v>
+        <v>7203981</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6436,7 +6420,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6446,7 +6430,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6473,10 +6457,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119537127</v>
+        <v>119536275</v>
       </c>
       <c r="B54" t="n">
-        <v>79642</v>
+        <v>79636</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6489,21 +6473,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6513,10 +6497,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>539441</v>
+        <v>539330</v>
       </c>
       <c r="R54" t="n">
-        <v>7203738</v>
+        <v>7204059</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6548,7 +6532,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6558,7 +6542,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6585,10 +6569,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119536645</v>
+        <v>119536026</v>
       </c>
       <c r="B55" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6601,34 +6585,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>539289</v>
+        <v>539337</v>
       </c>
       <c r="R55" t="n">
-        <v>7204141</v>
+        <v>7203986</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6660,7 +6649,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6670,7 +6659,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6697,10 +6686,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119536028</v>
+        <v>119535949</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>104994</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6709,43 +6698,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539414</v>
+        <v>539400</v>
       </c>
       <c r="R56" t="n">
-        <v>7203683</v>
+        <v>7203837</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6777,7 +6761,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6787,7 +6771,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6814,10 +6798,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119536274</v>
+        <v>119536520</v>
       </c>
       <c r="B57" t="n">
-        <v>79636</v>
+        <v>96862</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6830,21 +6814,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6854,10 +6838,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539353</v>
+        <v>539260</v>
       </c>
       <c r="R57" t="n">
-        <v>7203981</v>
+        <v>7203982</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6889,7 +6873,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6899,7 +6883,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6926,10 +6910,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119536276</v>
+        <v>119536340</v>
       </c>
       <c r="B58" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6938,25 +6922,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6966,10 +6950,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>539490</v>
+        <v>539325</v>
       </c>
       <c r="R58" t="n">
-        <v>7203595</v>
+        <v>7204093</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7001,7 +6985,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7011,7 +6995,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7038,10 +7022,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119537126</v>
+        <v>119536004</v>
       </c>
       <c r="B59" t="n">
-        <v>79642</v>
+        <v>90562</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7050,25 +7034,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7078,10 +7062,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>539504</v>
+        <v>539306</v>
       </c>
       <c r="R59" t="n">
-        <v>7203691</v>
+        <v>7204149</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7113,7 +7097,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7123,7 +7107,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7150,10 +7134,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119536619</v>
+        <v>119536717</v>
       </c>
       <c r="B60" t="n">
-        <v>94311</v>
+        <v>80483</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7162,25 +7146,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2809</v>
+        <v>1049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7190,10 +7174,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>539501</v>
+        <v>539314</v>
       </c>
       <c r="R60" t="n">
-        <v>7203654</v>
+        <v>7203905</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7225,7 +7209,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7235,7 +7219,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7262,10 +7246,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119536333</v>
+        <v>119536900</v>
       </c>
       <c r="B61" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7278,21 +7262,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7302,10 +7286,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>539410</v>
+        <v>539326</v>
       </c>
       <c r="R61" t="n">
-        <v>7203877</v>
+        <v>7204101</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7337,7 +7321,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7347,7 +7331,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7374,10 +7358,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119536879</v>
+        <v>119537126</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>79642</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7386,20 +7370,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7414,10 +7398,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>539500</v>
+        <v>539504</v>
       </c>
       <c r="R62" t="n">
-        <v>7203672</v>
+        <v>7203691</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7449,7 +7433,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7459,7 +7443,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7486,10 +7470,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119536495</v>
+        <v>119536269</v>
       </c>
       <c r="B63" t="n">
-        <v>90846</v>
+        <v>79636</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7498,25 +7482,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7526,10 +7510,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>539325</v>
+        <v>539518</v>
       </c>
       <c r="R63" t="n">
-        <v>7204093</v>
+        <v>7203548</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7561,7 +7545,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7571,7 +7555,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7598,10 +7582,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119537048</v>
+        <v>119536805</v>
       </c>
       <c r="B64" t="n">
-        <v>90043</v>
+        <v>90580</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7614,21 +7598,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3286</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7638,10 +7622,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>539427</v>
+        <v>539529</v>
       </c>
       <c r="R64" t="n">
-        <v>7203770</v>
+        <v>7203613</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7673,7 +7657,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7683,7 +7667,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7710,10 +7694,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119536889</v>
+        <v>119537048</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>90043</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7726,21 +7710,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>3286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7750,10 +7734,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>539408</v>
+        <v>539427</v>
       </c>
       <c r="R65" t="n">
-        <v>7203874</v>
+        <v>7203770</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7785,7 +7769,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7795,7 +7779,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7822,7 +7806,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119536909</v>
+        <v>119536874</v>
       </c>
       <c r="B66" t="n">
         <v>78526</v>
@@ -7862,10 +7846,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>539260</v>
+        <v>539525</v>
       </c>
       <c r="R66" t="n">
-        <v>7203982</v>
+        <v>7203611</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7897,7 +7881,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7907,7 +7891,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7934,10 +7918,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119536908</v>
+        <v>119535950</v>
       </c>
       <c r="B67" t="n">
-        <v>78526</v>
+        <v>104994</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7946,25 +7930,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7974,10 +7958,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>539246</v>
+        <v>539261</v>
       </c>
       <c r="R67" t="n">
-        <v>7203987</v>
+        <v>7203983</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8009,7 +7993,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8019,7 +8003,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8046,10 +8030,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119536270</v>
+        <v>119536904</v>
       </c>
       <c r="B68" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8058,25 +8042,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8086,10 +8070,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>539441</v>
+        <v>539309</v>
       </c>
       <c r="R68" t="n">
-        <v>7203738</v>
+        <v>7204157</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8121,7 +8105,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8131,7 +8115,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8158,10 +8142,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119536684</v>
+        <v>119536879</v>
       </c>
       <c r="B69" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8170,25 +8154,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8198,10 +8182,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>539409</v>
+        <v>539500</v>
       </c>
       <c r="R69" t="n">
-        <v>7203733</v>
+        <v>7203672</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8233,7 +8217,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8243,7 +8227,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8270,10 +8254,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119536683</v>
+        <v>119536002</v>
       </c>
       <c r="B70" t="n">
-        <v>79643</v>
+        <v>90562</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8282,25 +8266,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8310,10 +8294,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>539259</v>
+        <v>539326</v>
       </c>
       <c r="R70" t="n">
-        <v>7203973</v>
+        <v>7204093</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8345,7 +8329,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8355,7 +8339,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8382,7 +8366,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119536882</v>
+        <v>119536892</v>
       </c>
       <c r="B71" t="n">
         <v>78526</v>
@@ -8422,10 +8406,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>539508</v>
+        <v>539346</v>
       </c>
       <c r="R71" t="n">
-        <v>7203755</v>
+        <v>7203934</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8457,7 +8441,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8467,7 +8451,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8494,10 +8478,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119536912</v>
+        <v>119537129</v>
       </c>
       <c r="B72" t="n">
-        <v>78526</v>
+        <v>79642</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8506,20 +8490,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8534,10 +8518,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>539412</v>
+        <v>539380</v>
       </c>
       <c r="R72" t="n">
-        <v>7203743</v>
+        <v>7203902</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8569,7 +8553,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8579,7 +8563,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8606,7 +8590,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119536904</v>
+        <v>119536875</v>
       </c>
       <c r="B73" t="n">
         <v>78526</v>
@@ -8646,10 +8630,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>539309</v>
+        <v>539503</v>
       </c>
       <c r="R73" t="n">
-        <v>7204157</v>
+        <v>7203619</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8681,7 +8665,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8691,7 +8675,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8718,10 +8702,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119536888</v>
+        <v>119537112</v>
       </c>
       <c r="B74" t="n">
-        <v>78526</v>
+        <v>91128</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8730,25 +8714,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8758,10 +8742,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>539404</v>
+        <v>539486</v>
       </c>
       <c r="R74" t="n">
-        <v>7203854</v>
+        <v>7203594</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8793,7 +8777,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8803,7 +8787,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8830,10 +8814,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119537245</v>
+        <v>119536806</v>
       </c>
       <c r="B75" t="n">
-        <v>90957</v>
+        <v>90580</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8842,25 +8826,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4217</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8870,10 +8854,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>539319</v>
+        <v>539337</v>
       </c>
       <c r="R75" t="n">
-        <v>7204161</v>
+        <v>7204110</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8905,7 +8889,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8915,7 +8899,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8942,10 +8926,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119536681</v>
+        <v>119536344</v>
       </c>
       <c r="B76" t="n">
-        <v>79643</v>
+        <v>79608</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8954,25 +8938,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8982,10 +8966,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>539381</v>
+        <v>539392</v>
       </c>
       <c r="R76" t="n">
-        <v>7203902</v>
+        <v>7203749</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9017,7 +9001,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9027,7 +9011,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9054,10 +9038,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119536405</v>
+        <v>119536873</v>
       </c>
       <c r="B77" t="n">
-        <v>79511</v>
+        <v>78526</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9066,25 +9050,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9094,10 +9078,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>539273</v>
+        <v>539528</v>
       </c>
       <c r="R77" t="n">
-        <v>7203974</v>
+        <v>7203612</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9129,7 +9113,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9139,7 +9123,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9166,10 +9150,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119536024</v>
+        <v>119536883</v>
       </c>
       <c r="B78" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9182,39 +9166,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>539515</v>
+        <v>539438</v>
       </c>
       <c r="R78" t="n">
-        <v>7203720</v>
+        <v>7203740</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9246,7 +9225,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9256,7 +9235,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9283,10 +9262,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119536025</v>
+        <v>119537130</v>
       </c>
       <c r="B79" t="n">
-        <v>57310</v>
+        <v>79642</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9295,43 +9274,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>539346</v>
+        <v>539259</v>
       </c>
       <c r="R79" t="n">
-        <v>7203957</v>
+        <v>7203973</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9363,7 +9337,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9373,7 +9347,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9400,10 +9374,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119536027</v>
+        <v>119536887</v>
       </c>
       <c r="B80" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9416,39 +9390,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>539326</v>
+        <v>539398</v>
       </c>
       <c r="R80" t="n">
-        <v>7204100</v>
+        <v>7203841</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9480,7 +9449,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9490,7 +9459,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9517,10 +9486,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119537112</v>
+        <v>119536890</v>
       </c>
       <c r="B81" t="n">
-        <v>91128</v>
+        <v>78526</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9529,25 +9498,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9557,10 +9526,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>539486</v>
+        <v>539381</v>
       </c>
       <c r="R81" t="n">
-        <v>7203594</v>
+        <v>7203909</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9592,7 +9561,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9602,7 +9571,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9629,10 +9598,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119536493</v>
+        <v>119536024</v>
       </c>
       <c r="B82" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9645,34 +9614,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>539429</v>
+        <v>539515</v>
       </c>
       <c r="R82" t="n">
-        <v>7203761</v>
+        <v>7203720</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9704,7 +9678,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9714,7 +9688,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9741,10 +9715,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119536005</v>
+        <v>119536097</v>
       </c>
       <c r="B83" t="n">
-        <v>90562</v>
+        <v>56522</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9753,38 +9727,54 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>539315</v>
+        <v>539309</v>
       </c>
       <c r="R83" t="n">
-        <v>7204159</v>
+        <v>7204157</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9816,7 +9806,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9826,7 +9816,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9853,10 +9843,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119536332</v>
+        <v>119536000</v>
       </c>
       <c r="B84" t="n">
-        <v>79608</v>
+        <v>90905</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9865,25 +9855,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>2062</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9893,10 +9883,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>539404</v>
+        <v>539319</v>
       </c>
       <c r="R84" t="n">
-        <v>7203853</v>
+        <v>7204161</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9928,7 +9918,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9938,7 +9928,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Troligen S. Delicata</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9949,6 +9944,21 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -9965,10 +9975,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119536401</v>
+        <v>119536341</v>
       </c>
       <c r="B85" t="n">
-        <v>99161</v>
+        <v>79608</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9977,25 +9987,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10005,10 +10015,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>539522</v>
+        <v>539268</v>
       </c>
       <c r="R85" t="n">
-        <v>7203617</v>
+        <v>7204021</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10040,7 +10050,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10050,7 +10060,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10077,7 +10087,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119536880</v>
+        <v>119536897</v>
       </c>
       <c r="B86" t="n">
         <v>78526</v>
@@ -10117,10 +10127,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>539505</v>
+        <v>539335</v>
       </c>
       <c r="R86" t="n">
-        <v>7203692</v>
+        <v>7204015</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10152,7 +10162,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10162,7 +10172,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10189,7 +10199,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119536910</v>
+        <v>119536870</v>
       </c>
       <c r="B87" t="n">
         <v>78526</v>
@@ -10229,10 +10239,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>539259</v>
+        <v>539517</v>
       </c>
       <c r="R87" t="n">
-        <v>7203973</v>
+        <v>7203551</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10264,7 +10274,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10274,7 +10284,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10301,10 +10311,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119536905</v>
+        <v>119536493</v>
       </c>
       <c r="B88" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10317,21 +10327,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10341,10 +10351,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>539319</v>
+        <v>539429</v>
       </c>
       <c r="R88" t="n">
-        <v>7204163</v>
+        <v>7203761</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10376,7 +10386,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10386,7 +10396,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10413,10 +10423,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119536878</v>
+        <v>119536406</v>
       </c>
       <c r="B89" t="n">
-        <v>78526</v>
+        <v>79511</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10425,25 +10435,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10453,10 +10463,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>539504</v>
+        <v>539285</v>
       </c>
       <c r="R89" t="n">
-        <v>7203658</v>
+        <v>7203971</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10488,7 +10498,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10498,7 +10508,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10525,10 +10535,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119536107</v>
+        <v>119536878</v>
       </c>
       <c r="B90" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10541,43 +10551,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>539353</v>
+        <v>539504</v>
       </c>
       <c r="R90" t="n">
-        <v>7203941</v>
+        <v>7203658</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10609,7 +10610,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10619,7 +10620,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10646,10 +10647,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119536717</v>
+        <v>119536107</v>
       </c>
       <c r="B91" t="n">
-        <v>80483</v>
+        <v>57463</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10662,34 +10663,43 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1049</v>
+        <v>103021</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>539314</v>
+        <v>539353</v>
       </c>
       <c r="R91" t="n">
-        <v>7203905</v>
+        <v>7203941</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10721,7 +10731,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10731,7 +10741,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10758,7 +10768,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119536765</v>
+        <v>119536764</v>
       </c>
       <c r="B92" t="n">
         <v>90558</v>
@@ -10798,10 +10808,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>539440</v>
+        <v>539508</v>
       </c>
       <c r="R92" t="n">
-        <v>7203703</v>
+        <v>7203557</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10833,7 +10843,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10843,7 +10853,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10870,10 +10880,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119536327</v>
+        <v>119536899</v>
       </c>
       <c r="B93" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10886,21 +10896,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10910,10 +10920,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>539506</v>
+        <v>539342</v>
       </c>
       <c r="R93" t="n">
-        <v>7203636</v>
+        <v>7204082</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10945,7 +10955,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10955,7 +10965,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10982,10 +10992,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119536273</v>
+        <v>119536021</v>
       </c>
       <c r="B94" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10994,38 +11004,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>539392</v>
+        <v>539499</v>
       </c>
       <c r="R94" t="n">
-        <v>7203821</v>
+        <v>7203671</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11057,7 +11072,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11067,7 +11082,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11094,10 +11109,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119536898</v>
+        <v>119536025</v>
       </c>
       <c r="B95" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11110,34 +11125,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>539330</v>
+        <v>539346</v>
       </c>
       <c r="R95" t="n">
-        <v>7204056</v>
+        <v>7203957</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11169,7 +11189,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11179,7 +11199,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11318,10 +11338,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119536335</v>
+        <v>119536910</v>
       </c>
       <c r="B97" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11334,21 +11354,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11358,10 +11378,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>539371</v>
+        <v>539259</v>
       </c>
       <c r="R97" t="n">
-        <v>7203932</v>
+        <v>7203973</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11393,7 +11413,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11403,7 +11423,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11430,10 +11450,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119536334</v>
+        <v>119536880</v>
       </c>
       <c r="B98" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11446,21 +11466,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11470,10 +11490,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>539383</v>
+        <v>539505</v>
       </c>
       <c r="R98" t="n">
-        <v>7203898</v>
+        <v>7203692</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11505,7 +11525,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11515,7 +11535,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11542,7 +11562,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119536885</v>
+        <v>119536906</v>
       </c>
       <c r="B99" t="n">
         <v>78526</v>
@@ -11582,10 +11602,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>539391</v>
+        <v>539291</v>
       </c>
       <c r="R99" t="n">
-        <v>7203788</v>
+        <v>7204141</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11617,7 +11637,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11627,7 +11647,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11654,10 +11674,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119536337</v>
+        <v>119536020</v>
       </c>
       <c r="B100" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11670,34 +11690,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>539338</v>
+        <v>539508</v>
       </c>
       <c r="R100" t="n">
-        <v>7203941</v>
+        <v>7203619</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11729,7 +11754,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11739,7 +11764,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11766,10 +11791,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119536343</v>
+        <v>119536707</v>
       </c>
       <c r="B101" t="n">
-        <v>79608</v>
+        <v>57421</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11778,38 +11803,47 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>539360</v>
+        <v>539474</v>
       </c>
       <c r="R101" t="n">
-        <v>7203797</v>
+        <v>7203674</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11841,7 +11875,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11851,7 +11885,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11878,10 +11912,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119536342</v>
+        <v>119536912</v>
       </c>
       <c r="B102" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11894,21 +11928,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11918,10 +11952,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>539259</v>
+        <v>539412</v>
       </c>
       <c r="R102" t="n">
-        <v>7203973</v>
+        <v>7203743</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11953,7 +11987,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11963,7 +11997,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11990,7 +12024,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119536890</v>
+        <v>119536877</v>
       </c>
       <c r="B103" t="n">
         <v>78526</v>
@@ -12030,10 +12064,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>539381</v>
+        <v>539504</v>
       </c>
       <c r="R103" t="n">
-        <v>7203909</v>
+        <v>7203633</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12065,7 +12099,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12075,7 +12109,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12102,10 +12136,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119536001</v>
+        <v>119537131</v>
       </c>
       <c r="B104" t="n">
-        <v>90562</v>
+        <v>79642</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12114,25 +12148,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12142,10 +12176,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>539342</v>
+        <v>539417</v>
       </c>
       <c r="R104" t="n">
-        <v>7204082</v>
+        <v>7203723</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12177,7 +12211,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12187,7 +12221,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12214,10 +12248,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119536790</v>
+        <v>119536270</v>
       </c>
       <c r="B105" t="n">
-        <v>90576</v>
+        <v>79636</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12226,25 +12260,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12254,10 +12288,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>539492</v>
+        <v>539441</v>
       </c>
       <c r="R105" t="n">
-        <v>7203590</v>
+        <v>7203738</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12289,7 +12323,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12299,7 +12333,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12326,10 +12360,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119536336</v>
+        <v>119536276</v>
       </c>
       <c r="B106" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12338,25 +12372,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12366,10 +12400,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>539352</v>
+        <v>539490</v>
       </c>
       <c r="R106" t="n">
-        <v>7203941</v>
+        <v>7203595</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12401,7 +12435,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12411,7 +12445,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12438,10 +12472,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119536907</v>
+        <v>119536027</v>
       </c>
       <c r="B107" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12454,34 +12488,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>539291</v>
+        <v>539326</v>
       </c>
       <c r="R107" t="n">
-        <v>7204060</v>
+        <v>7204100</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12513,7 +12552,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12523,7 +12562,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12550,7 +12589,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119536896</v>
+        <v>119536909</v>
       </c>
       <c r="B108" t="n">
         <v>78526</v>
@@ -12590,10 +12629,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>539337</v>
+        <v>539260</v>
       </c>
       <c r="R108" t="n">
-        <v>7203986</v>
+        <v>7203982</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12625,7 +12664,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12635,7 +12674,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12662,10 +12701,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119536895</v>
+        <v>119536483</v>
       </c>
       <c r="B109" t="n">
-        <v>78526</v>
+        <v>91005</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12674,25 +12713,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12702,10 +12741,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>539355</v>
+        <v>539427</v>
       </c>
       <c r="R109" t="n">
-        <v>7203976</v>
+        <v>7203755</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12737,7 +12776,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12747,7 +12786,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12774,10 +12813,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119537130</v>
+        <v>119536495</v>
       </c>
       <c r="B110" t="n">
-        <v>79642</v>
+        <v>90846</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12786,25 +12825,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12814,10 +12853,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>539259</v>
+        <v>539325</v>
       </c>
       <c r="R110" t="n">
-        <v>7203973</v>
+        <v>7204093</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12849,7 +12888,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12859,7 +12898,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12886,10 +12925,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119536269</v>
+        <v>119536886</v>
       </c>
       <c r="B111" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12898,25 +12937,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12926,10 +12965,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>539518</v>
+        <v>539387</v>
       </c>
       <c r="R111" t="n">
-        <v>7203548</v>
+        <v>7203818</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -12961,7 +13000,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12971,7 +13010,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12998,7 +13037,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119536875</v>
+        <v>119536902</v>
       </c>
       <c r="B112" t="n">
         <v>78526</v>
@@ -13038,10 +13077,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>539503</v>
+        <v>539340</v>
       </c>
       <c r="R112" t="n">
-        <v>7203619</v>
+        <v>7204108</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -13073,7 +13112,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13083,7 +13122,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13110,10 +13149,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119536913</v>
+        <v>119537142</v>
       </c>
       <c r="B113" t="n">
-        <v>78526</v>
+        <v>74630</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13126,21 +13165,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13150,10 +13189,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>539418</v>
+        <v>539514</v>
       </c>
       <c r="R113" t="n">
-        <v>7203718</v>
+        <v>7203719</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -13185,7 +13224,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13195,7 +13234,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13222,7 +13261,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119536906</v>
+        <v>119536891</v>
       </c>
       <c r="B114" t="n">
         <v>78526</v>
@@ -13262,10 +13301,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>539291</v>
+        <v>539381</v>
       </c>
       <c r="R114" t="n">
-        <v>7204141</v>
+        <v>7203929</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -13297,7 +13336,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13307,7 +13346,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13334,7 +13373,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119536877</v>
+        <v>119536895</v>
       </c>
       <c r="B115" t="n">
         <v>78526</v>
@@ -13374,10 +13413,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>539504</v>
+        <v>539355</v>
       </c>
       <c r="R115" t="n">
-        <v>7203633</v>
+        <v>7203976</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -13409,7 +13448,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13419,7 +13458,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13446,10 +13485,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119536406</v>
+        <v>119536007</v>
       </c>
       <c r="B116" t="n">
-        <v>79511</v>
+        <v>90562</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13458,25 +13497,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13486,10 +13525,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>539285</v>
+        <v>539248</v>
       </c>
       <c r="R116" t="n">
-        <v>7203971</v>
+        <v>7203984</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13521,7 +13560,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13531,7 +13570,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13558,10 +13597,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119537142</v>
+        <v>119536889</v>
       </c>
       <c r="B117" t="n">
-        <v>74630</v>
+        <v>78526</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13574,21 +13613,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13598,10 +13637,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>539514</v>
+        <v>539408</v>
       </c>
       <c r="R117" t="n">
-        <v>7203719</v>
+        <v>7203874</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13633,7 +13672,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13643,7 +13682,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13670,10 +13709,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119536347</v>
+        <v>119536885</v>
       </c>
       <c r="B118" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13686,21 +13725,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13710,10 +13749,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>539474</v>
+        <v>539391</v>
       </c>
       <c r="R118" t="n">
-        <v>7203607</v>
+        <v>7203788</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13745,7 +13784,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13755,7 +13794,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13782,10 +13821,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119536330</v>
+        <v>119536898</v>
       </c>
       <c r="B119" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13798,21 +13837,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13822,10 +13861,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>539440</v>
+        <v>539330</v>
       </c>
       <c r="R119" t="n">
-        <v>7203741</v>
+        <v>7204056</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13857,7 +13896,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13867,7 +13906,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13894,10 +13933,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119536777</v>
+        <v>119536907</v>
       </c>
       <c r="B120" t="n">
-        <v>74622</v>
+        <v>78526</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13906,25 +13945,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13934,10 +13973,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>539510</v>
+        <v>539291</v>
       </c>
       <c r="R120" t="n">
-        <v>7203622</v>
+        <v>7204060</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13969,7 +14008,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13979,7 +14018,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14006,10 +14045,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119536893</v>
+        <v>119536001</v>
       </c>
       <c r="B121" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14022,21 +14061,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14046,10 +14085,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>539338</v>
+        <v>539342</v>
       </c>
       <c r="R121" t="n">
-        <v>7203941</v>
+        <v>7204082</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -14081,7 +14120,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14091,7 +14130,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14118,10 +14157,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119536876</v>
+        <v>119536765</v>
       </c>
       <c r="B122" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14134,21 +14173,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14158,10 +14197,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>539520</v>
+        <v>539440</v>
       </c>
       <c r="R122" t="n">
-        <v>7203615</v>
+        <v>7203703</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14193,7 +14232,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14203,7 +14242,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14230,10 +14269,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119536899</v>
+        <v>119537245</v>
       </c>
       <c r="B123" t="n">
-        <v>78526</v>
+        <v>90957</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14242,25 +14281,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14270,10 +14309,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>539342</v>
+        <v>539319</v>
       </c>
       <c r="R123" t="n">
-        <v>7204082</v>
+        <v>7204161</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14305,7 +14344,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14315,7 +14354,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14342,10 +14381,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119536275</v>
+        <v>119536915</v>
       </c>
       <c r="B124" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14354,25 +14393,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14382,10 +14421,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>539330</v>
+        <v>539474</v>
       </c>
       <c r="R124" t="n">
-        <v>7204059</v>
+        <v>7203605</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -14417,7 +14456,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14427,7 +14466,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14454,10 +14493,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119537128</v>
+        <v>119536908</v>
       </c>
       <c r="B125" t="n">
-        <v>79642</v>
+        <v>78526</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14466,20 +14505,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -14494,10 +14533,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>539389</v>
+        <v>539246</v>
       </c>
       <c r="R125" t="n">
-        <v>7203822</v>
+        <v>7203987</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14529,7 +14568,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14539,7 +14578,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14566,10 +14605,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119536712</v>
+        <v>119536888</v>
       </c>
       <c r="B126" t="n">
-        <v>90954</v>
+        <v>78526</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14582,32 +14621,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>539391</v>
+        <v>539404</v>
       </c>
       <c r="R126" t="n">
-        <v>7203790</v>
+        <v>7203854</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14639,7 +14680,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14649,7 +14690,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14658,7 +14699,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -14677,10 +14717,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119536784</v>
+        <v>119536876</v>
       </c>
       <c r="B127" t="n">
-        <v>97806</v>
+        <v>78526</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14689,25 +14729,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219795</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14717,10 +14757,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>539347</v>
+        <v>539520</v>
       </c>
       <c r="R127" t="n">
-        <v>7203938</v>
+        <v>7203615</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14752,7 +14792,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14762,7 +14802,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14789,10 +14829,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119536483</v>
+        <v>119536754</v>
       </c>
       <c r="B128" t="n">
-        <v>91005</v>
+        <v>56514</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14801,38 +14841,47 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>539427</v>
+        <v>539402</v>
       </c>
       <c r="R128" t="n">
-        <v>7203755</v>
+        <v>7203785</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14864,7 +14913,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14874,7 +14923,12 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Familjegrupp</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14901,10 +14955,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119536096</v>
+        <v>119536333</v>
       </c>
       <c r="B129" t="n">
-        <v>56522</v>
+        <v>79608</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14913,42 +14967,38 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>539506</v>
+        <v>539410</v>
       </c>
       <c r="R129" t="n">
-        <v>7203636</v>
+        <v>7203877</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14980,7 +15030,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14990,7 +15040,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15017,10 +15067,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119536097</v>
+        <v>119536338</v>
       </c>
       <c r="B130" t="n">
-        <v>56522</v>
+        <v>79608</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15029,54 +15079,38 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>539309</v>
+        <v>539333</v>
       </c>
       <c r="R130" t="n">
-        <v>7204157</v>
+        <v>7204016</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -15108,7 +15142,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15118,7 +15152,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15145,10 +15179,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119536716</v>
+        <v>119536346</v>
       </c>
       <c r="B131" t="n">
-        <v>80483</v>
+        <v>79608</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15161,21 +15195,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1049</v>
+        <v>2081</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15185,10 +15219,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>539315</v>
+        <v>539419</v>
       </c>
       <c r="R131" t="n">
-        <v>7203955</v>
+        <v>7203720</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -15220,7 +15254,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15230,7 +15264,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15257,10 +15291,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119536554</v>
+        <v>119536336</v>
       </c>
       <c r="B132" t="n">
-        <v>90916</v>
+        <v>79608</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15269,25 +15303,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1506</v>
+        <v>2081</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15297,10 +15331,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>539431</v>
+        <v>539352</v>
       </c>
       <c r="R132" t="n">
-        <v>7203761</v>
+        <v>7203941</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -15332,7 +15366,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15342,7 +15376,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15369,7 +15403,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119536914</v>
+        <v>119536911</v>
       </c>
       <c r="B133" t="n">
         <v>78526</v>
@@ -15409,10 +15443,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>539438</v>
+        <v>539314</v>
       </c>
       <c r="R133" t="n">
-        <v>7203711</v>
+        <v>7203905</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -15444,7 +15478,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15454,7 +15488,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15481,10 +15515,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119536682</v>
+        <v>119536914</v>
       </c>
       <c r="B134" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15493,25 +15527,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15521,10 +15555,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>539270</v>
+        <v>539438</v>
       </c>
       <c r="R134" t="n">
-        <v>7204025</v>
+        <v>7203711</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -15556,7 +15590,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15566,7 +15600,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15593,10 +15627,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119536000</v>
+        <v>119536905</v>
       </c>
       <c r="B135" t="n">
-        <v>90905</v>
+        <v>78526</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15605,25 +15639,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15636,7 +15670,7 @@
         <v>539319</v>
       </c>
       <c r="R135" t="n">
-        <v>7204161</v>
+        <v>7204163</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -15668,7 +15702,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15678,12 +15712,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Troligen S. Delicata</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15694,21 +15723,6 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
@@ -15725,10 +15739,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119536340</v>
+        <v>119536685</v>
       </c>
       <c r="B136" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15737,25 +15751,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15765,10 +15779,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>539325</v>
+        <v>539419</v>
       </c>
       <c r="R136" t="n">
-        <v>7204093</v>
+        <v>7203720</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15800,7 +15814,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15810,7 +15824,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15837,10 +15851,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119536339</v>
+        <v>119536684</v>
       </c>
       <c r="B137" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15849,25 +15863,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15877,10 +15891,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>539330</v>
+        <v>539409</v>
       </c>
       <c r="R137" t="n">
-        <v>7204058</v>
+        <v>7203733</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -15912,7 +15926,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15922,7 +15936,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15949,10 +15963,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119536754</v>
+        <v>119536872</v>
       </c>
       <c r="B138" t="n">
-        <v>56514</v>
+        <v>78526</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15965,43 +15979,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>539402</v>
+        <v>539509</v>
       </c>
       <c r="R138" t="n">
-        <v>7203785</v>
+        <v>7203558</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -16033,7 +16038,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16043,12 +16048,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>17:02</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Familjegrupp</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16075,10 +16075,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119536004</v>
+        <v>119536894</v>
       </c>
       <c r="B139" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16091,21 +16091,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16115,10 +16115,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>539306</v>
+        <v>539344</v>
       </c>
       <c r="R139" t="n">
-        <v>7204149</v>
+        <v>7203950</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16187,10 +16187,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119536002</v>
+        <v>119536903</v>
       </c>
       <c r="B140" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16203,21 +16203,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -16227,10 +16227,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>539326</v>
+        <v>539306</v>
       </c>
       <c r="R140" t="n">
-        <v>7204093</v>
+        <v>7204148</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -16262,7 +16262,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16299,10 +16299,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119536329</v>
+        <v>119536716</v>
       </c>
       <c r="B141" t="n">
-        <v>79608</v>
+        <v>80483</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16315,21 +16315,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2081</v>
+        <v>1049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16339,10 +16339,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>539508</v>
+        <v>539315</v>
       </c>
       <c r="R141" t="n">
-        <v>7203755</v>
+        <v>7203955</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -16374,7 +16374,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16384,7 +16384,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16411,10 +16411,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119535969</v>
+        <v>119536913</v>
       </c>
       <c r="B142" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16427,21 +16427,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16451,10 +16451,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>539512</v>
+        <v>539418</v>
       </c>
       <c r="R142" t="n">
-        <v>7203549</v>
+        <v>7203718</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -16486,7 +16486,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16496,7 +16496,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16523,10 +16523,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119536897</v>
+        <v>119537248</v>
       </c>
       <c r="B143" t="n">
-        <v>78526</v>
+        <v>77910</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16539,21 +16539,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16563,10 +16563,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>539335</v>
+        <v>539311</v>
       </c>
       <c r="R143" t="n">
-        <v>7204015</v>
+        <v>7203961</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16635,10 +16635,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119536894</v>
+        <v>119536680</v>
       </c>
       <c r="B144" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16647,25 +16647,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16675,10 +16675,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>539344</v>
+        <v>539505</v>
       </c>
       <c r="R144" t="n">
-        <v>7203950</v>
+        <v>7203636</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16747,10 +16747,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119536680</v>
+        <v>119536331</v>
       </c>
       <c r="B145" t="n">
-        <v>79643</v>
+        <v>79608</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16759,25 +16759,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16787,10 +16787,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>539505</v>
+        <v>539389</v>
       </c>
       <c r="R145" t="n">
-        <v>7203636</v>
+        <v>7203819</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -16822,7 +16822,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16832,7 +16832,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16859,10 +16859,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119537149</v>
+        <v>119536334</v>
       </c>
       <c r="B146" t="n">
-        <v>77458</v>
+        <v>79608</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16875,21 +16875,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6487</v>
+        <v>2081</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16899,10 +16899,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>539312</v>
+        <v>539383</v>
       </c>
       <c r="R146" t="n">
-        <v>7203957</v>
+        <v>7203898</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16944,7 +16944,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD146" t="b">

--- a/artfynd/A 28725-2024 artfynd.xlsx
+++ b/artfynd/A 28725-2024 artfynd.xlsx
@@ -2752,10 +2752,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119536790</v>
+        <v>119536339</v>
       </c>
       <c r="B21" t="n">
-        <v>90576</v>
+        <v>79608</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2768,21 +2768,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>539492</v>
+        <v>539330</v>
       </c>
       <c r="R21" t="n">
-        <v>7203590</v>
+        <v>7204058</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2864,10 +2864,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119535983</v>
+        <v>119536790</v>
       </c>
       <c r="B22" t="n">
-        <v>90527</v>
+        <v>90576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2876,25 +2876,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>539249</v>
+        <v>539492</v>
       </c>
       <c r="R22" t="n">
-        <v>7203985</v>
+        <v>7203590</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2976,10 +2976,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119536777</v>
+        <v>119535983</v>
       </c>
       <c r="B23" t="n">
-        <v>74622</v>
+        <v>90527</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2992,21 +2992,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6439</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>539510</v>
+        <v>539249</v>
       </c>
       <c r="R23" t="n">
-        <v>7203622</v>
+        <v>7203985</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3088,10 +3088,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119535969</v>
+        <v>119536619</v>
       </c>
       <c r="B24" t="n">
-        <v>74638</v>
+        <v>94311</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3100,25 +3100,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>539512</v>
+        <v>539501</v>
       </c>
       <c r="R24" t="n">
-        <v>7203549</v>
+        <v>7203654</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3200,10 +3200,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119537149</v>
+        <v>119536327</v>
       </c>
       <c r="B25" t="n">
-        <v>77458</v>
+        <v>79608</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3216,21 +3216,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3240,10 +3240,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>539312</v>
+        <v>539506</v>
       </c>
       <c r="R25" t="n">
-        <v>7203957</v>
+        <v>7203636</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3312,10 +3312,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119537128</v>
+        <v>119536777</v>
       </c>
       <c r="B26" t="n">
-        <v>79642</v>
+        <v>74622</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3328,21 +3328,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>6439</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>539389</v>
+        <v>539510</v>
       </c>
       <c r="R26" t="n">
-        <v>7203822</v>
+        <v>7203622</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3424,10 +3424,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119536273</v>
+        <v>119535969</v>
       </c>
       <c r="B27" t="n">
-        <v>79636</v>
+        <v>74638</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3436,25 +3436,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3464,10 +3464,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>539392</v>
+        <v>539512</v>
       </c>
       <c r="R27" t="n">
-        <v>7203821</v>
+        <v>7203549</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3536,10 +3536,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119536619</v>
+        <v>119537149</v>
       </c>
       <c r="B28" t="n">
-        <v>94311</v>
+        <v>77458</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3548,25 +3548,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2809</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>539501</v>
+        <v>539312</v>
       </c>
       <c r="R28" t="n">
-        <v>7203654</v>
+        <v>7203957</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3648,10 +3648,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119536339</v>
+        <v>119537128</v>
       </c>
       <c r="B29" t="n">
-        <v>79608</v>
+        <v>79642</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3660,25 +3660,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>539330</v>
+        <v>539389</v>
       </c>
       <c r="R29" t="n">
-        <v>7204058</v>
+        <v>7203822</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3760,10 +3760,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119536327</v>
+        <v>119536273</v>
       </c>
       <c r="B30" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3772,25 +3772,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>539506</v>
+        <v>539392</v>
       </c>
       <c r="R30" t="n">
-        <v>7203636</v>
+        <v>7203821</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3984,10 +3984,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119536028</v>
+        <v>119536871</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4000,39 +4000,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>539414</v>
+        <v>539512</v>
       </c>
       <c r="R32" t="n">
-        <v>7203683</v>
+        <v>7203548</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4064,7 +4059,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4074,7 +4069,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4213,10 +4208,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119536871</v>
+        <v>119536028</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4229,34 +4224,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>539512</v>
+        <v>539414</v>
       </c>
       <c r="R34" t="n">
-        <v>7203548</v>
+        <v>7203683</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4325,10 +4325,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536893</v>
+        <v>119536348</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4341,21 +4341,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>539338</v>
+        <v>539466</v>
       </c>
       <c r="R35" t="n">
-        <v>7203941</v>
+        <v>7203618</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4437,7 +4437,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536348</v>
+        <v>119536332</v>
       </c>
       <c r="B36" t="n">
         <v>79608</v>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>539466</v>
+        <v>539404</v>
       </c>
       <c r="R36" t="n">
-        <v>7203618</v>
+        <v>7203853</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4549,7 +4549,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119536332</v>
+        <v>119536330</v>
       </c>
       <c r="B37" t="n">
         <v>79608</v>
@@ -4589,10 +4589,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>539404</v>
+        <v>539440</v>
       </c>
       <c r="R37" t="n">
-        <v>7203853</v>
+        <v>7203741</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4661,10 +4661,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119536330</v>
+        <v>119536893</v>
       </c>
       <c r="B38" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4677,21 +4677,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539440</v>
+        <v>539338</v>
       </c>
       <c r="R38" t="n">
-        <v>7203741</v>
+        <v>7203941</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4773,10 +4773,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119536003</v>
+        <v>119536683</v>
       </c>
       <c r="B39" t="n">
-        <v>90562</v>
+        <v>79643</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4785,25 +4785,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539322</v>
+        <v>539259</v>
       </c>
       <c r="R39" t="n">
-        <v>7204109</v>
+        <v>7203973</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4885,10 +4885,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119536096</v>
+        <v>119536405</v>
       </c>
       <c r="B40" t="n">
-        <v>56522</v>
+        <v>79511</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4901,38 +4901,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539506</v>
+        <v>539273</v>
       </c>
       <c r="R40" t="n">
-        <v>7203636</v>
+        <v>7203974</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4964,7 +4960,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4974,7 +4970,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5001,10 +4997,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119537029</v>
+        <v>119536645</v>
       </c>
       <c r="B41" t="n">
-        <v>82305</v>
+        <v>79607</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5017,21 +5013,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5041,10 +5037,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>539525</v>
+        <v>539289</v>
       </c>
       <c r="R41" t="n">
-        <v>7203612</v>
+        <v>7204141</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5076,7 +5072,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5086,7 +5082,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5113,10 +5109,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119536683</v>
+        <v>119537029</v>
       </c>
       <c r="B42" t="n">
-        <v>79643</v>
+        <v>82305</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5125,25 +5121,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5153,10 +5149,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>539259</v>
+        <v>539525</v>
       </c>
       <c r="R42" t="n">
-        <v>7203973</v>
+        <v>7203612</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5188,7 +5184,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5198,7 +5194,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5225,10 +5221,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119536405</v>
+        <v>119536003</v>
       </c>
       <c r="B43" t="n">
-        <v>79511</v>
+        <v>90562</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5237,25 +5233,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5265,10 +5261,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>539273</v>
+        <v>539322</v>
       </c>
       <c r="R43" t="n">
-        <v>7203974</v>
+        <v>7204109</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5300,7 +5296,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5310,7 +5306,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5337,10 +5333,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119536645</v>
+        <v>119536096</v>
       </c>
       <c r="B44" t="n">
-        <v>79607</v>
+        <v>56522</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5349,38 +5345,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>539289</v>
+        <v>539506</v>
       </c>
       <c r="R44" t="n">
-        <v>7204141</v>
+        <v>7203636</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5449,10 +5449,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119536343</v>
+        <v>119536681</v>
       </c>
       <c r="B45" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5461,25 +5461,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>539360</v>
+        <v>539381</v>
       </c>
       <c r="R45" t="n">
-        <v>7203797</v>
+        <v>7203902</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5561,10 +5561,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119536403</v>
+        <v>119536343</v>
       </c>
       <c r="B46" t="n">
-        <v>94323</v>
+        <v>79608</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5573,25 +5573,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2813</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>539514</v>
+        <v>539360</v>
       </c>
       <c r="R46" t="n">
-        <v>7203744</v>
+        <v>7203797</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5673,10 +5673,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119536681</v>
+        <v>119536403</v>
       </c>
       <c r="B47" t="n">
-        <v>79643</v>
+        <v>94323</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5689,21 +5689,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>2813</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>539381</v>
+        <v>539514</v>
       </c>
       <c r="R47" t="n">
-        <v>7203902</v>
+        <v>7203744</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7022,10 +7022,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119536004</v>
+        <v>119537048</v>
       </c>
       <c r="B59" t="n">
-        <v>90562</v>
+        <v>90043</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7038,21 +7038,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>3286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>539306</v>
+        <v>539427</v>
       </c>
       <c r="R59" t="n">
-        <v>7204149</v>
+        <v>7203770</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7246,7 +7246,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119536900</v>
+        <v>119536874</v>
       </c>
       <c r="B61" t="n">
         <v>78526</v>
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>539326</v>
+        <v>539525</v>
       </c>
       <c r="R61" t="n">
-        <v>7204101</v>
+        <v>7203611</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7358,10 +7358,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119537126</v>
+        <v>119536900</v>
       </c>
       <c r="B62" t="n">
-        <v>79642</v>
+        <v>78526</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7370,20 +7370,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>539504</v>
+        <v>539326</v>
       </c>
       <c r="R62" t="n">
-        <v>7203691</v>
+        <v>7204101</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7470,10 +7470,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119536269</v>
+        <v>119537126</v>
       </c>
       <c r="B63" t="n">
-        <v>79636</v>
+        <v>79642</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7486,21 +7486,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7510,10 +7510,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>539518</v>
+        <v>539504</v>
       </c>
       <c r="R63" t="n">
-        <v>7203548</v>
+        <v>7203691</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7582,10 +7582,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119536805</v>
+        <v>119536269</v>
       </c>
       <c r="B64" t="n">
-        <v>90580</v>
+        <v>79636</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7594,25 +7594,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7622,10 +7622,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>539529</v>
+        <v>539518</v>
       </c>
       <c r="R64" t="n">
-        <v>7203613</v>
+        <v>7203548</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7694,10 +7694,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119537048</v>
+        <v>119536805</v>
       </c>
       <c r="B65" t="n">
-        <v>90043</v>
+        <v>90580</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7710,21 +7710,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3286</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7734,10 +7734,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>539427</v>
+        <v>539529</v>
       </c>
       <c r="R65" t="n">
-        <v>7203770</v>
+        <v>7203613</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7806,10 +7806,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119536874</v>
+        <v>119536004</v>
       </c>
       <c r="B66" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7822,21 +7822,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7846,10 +7846,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>539525</v>
+        <v>539306</v>
       </c>
       <c r="R66" t="n">
-        <v>7203611</v>
+        <v>7204149</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8030,10 +8030,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119536904</v>
+        <v>119537129</v>
       </c>
       <c r="B68" t="n">
-        <v>78526</v>
+        <v>79642</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8042,20 +8042,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8070,10 +8070,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>539309</v>
+        <v>539380</v>
       </c>
       <c r="R68" t="n">
-        <v>7204157</v>
+        <v>7203902</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8142,10 +8142,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119536879</v>
+        <v>119536002</v>
       </c>
       <c r="B69" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8158,21 +8158,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8182,10 +8182,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>539500</v>
+        <v>539326</v>
       </c>
       <c r="R69" t="n">
-        <v>7203672</v>
+        <v>7204093</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8217,7 +8217,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8254,10 +8254,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119536002</v>
+        <v>119536904</v>
       </c>
       <c r="B70" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8270,21 +8270,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>539326</v>
+        <v>539309</v>
       </c>
       <c r="R70" t="n">
-        <v>7204093</v>
+        <v>7204157</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8329,7 +8329,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8366,7 +8366,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119536892</v>
+        <v>119536879</v>
       </c>
       <c r="B71" t="n">
         <v>78526</v>
@@ -8406,10 +8406,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>539346</v>
+        <v>539500</v>
       </c>
       <c r="R71" t="n">
-        <v>7203934</v>
+        <v>7203672</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8478,10 +8478,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119537129</v>
+        <v>119536892</v>
       </c>
       <c r="B72" t="n">
-        <v>79642</v>
+        <v>78526</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8490,20 +8490,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8518,10 +8518,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>539380</v>
+        <v>539346</v>
       </c>
       <c r="R72" t="n">
-        <v>7203902</v>
+        <v>7203934</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8553,7 +8553,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9975,10 +9975,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119536341</v>
+        <v>119536897</v>
       </c>
       <c r="B85" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9991,21 +9991,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10015,10 +10015,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>539268</v>
+        <v>539335</v>
       </c>
       <c r="R85" t="n">
-        <v>7204021</v>
+        <v>7204015</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10087,7 +10087,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119536897</v>
+        <v>119536870</v>
       </c>
       <c r="B86" t="n">
         <v>78526</v>
@@ -10127,10 +10127,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>539335</v>
+        <v>539517</v>
       </c>
       <c r="R86" t="n">
-        <v>7204015</v>
+        <v>7203551</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10199,10 +10199,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119536870</v>
+        <v>119536406</v>
       </c>
       <c r="B87" t="n">
-        <v>78526</v>
+        <v>79511</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10211,25 +10211,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10239,10 +10239,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>539517</v>
+        <v>539285</v>
       </c>
       <c r="R87" t="n">
-        <v>7203551</v>
+        <v>7203971</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10311,10 +10311,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119536493</v>
+        <v>119536878</v>
       </c>
       <c r="B88" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10327,21 +10327,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10351,10 +10351,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>539429</v>
+        <v>539504</v>
       </c>
       <c r="R88" t="n">
-        <v>7203761</v>
+        <v>7203658</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10423,10 +10423,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119536406</v>
+        <v>119536341</v>
       </c>
       <c r="B89" t="n">
-        <v>79511</v>
+        <v>79608</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10435,25 +10435,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10463,10 +10463,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>539285</v>
+        <v>539268</v>
       </c>
       <c r="R89" t="n">
-        <v>7203971</v>
+        <v>7204021</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10535,10 +10535,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119536878</v>
+        <v>119536493</v>
       </c>
       <c r="B90" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10551,21 +10551,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10575,10 +10575,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>539504</v>
+        <v>539429</v>
       </c>
       <c r="R90" t="n">
-        <v>7203658</v>
+        <v>7203761</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10647,10 +10647,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119536107</v>
+        <v>119536899</v>
       </c>
       <c r="B91" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10663,43 +10663,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>539353</v>
+        <v>539342</v>
       </c>
       <c r="R91" t="n">
-        <v>7203941</v>
+        <v>7204082</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10731,7 +10722,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10741,7 +10732,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10768,10 +10759,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119536764</v>
+        <v>119536107</v>
       </c>
       <c r="B92" t="n">
-        <v>90558</v>
+        <v>57463</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10784,34 +10775,43 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>539508</v>
+        <v>539353</v>
       </c>
       <c r="R92" t="n">
-        <v>7203557</v>
+        <v>7203941</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10880,10 +10880,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119536899</v>
+        <v>119536764</v>
       </c>
       <c r="B93" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10896,21 +10896,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10920,10 +10920,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>539342</v>
+        <v>539508</v>
       </c>
       <c r="R93" t="n">
-        <v>7204082</v>
+        <v>7203557</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11226,10 +11226,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119536881</v>
+        <v>119536020</v>
       </c>
       <c r="B96" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11242,34 +11242,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>539513</v>
+        <v>539508</v>
       </c>
       <c r="R96" t="n">
-        <v>7203718</v>
+        <v>7203619</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11301,7 +11306,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11311,7 +11316,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11338,7 +11343,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119536910</v>
+        <v>119536880</v>
       </c>
       <c r="B97" t="n">
         <v>78526</v>
@@ -11378,10 +11383,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>539259</v>
+        <v>539505</v>
       </c>
       <c r="R97" t="n">
-        <v>7203973</v>
+        <v>7203692</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11413,7 +11418,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11423,7 +11428,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11450,7 +11455,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119536880</v>
+        <v>119536906</v>
       </c>
       <c r="B98" t="n">
         <v>78526</v>
@@ -11490,10 +11495,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>539505</v>
+        <v>539291</v>
       </c>
       <c r="R98" t="n">
-        <v>7203692</v>
+        <v>7204141</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11525,7 +11530,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11535,7 +11540,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11562,7 +11567,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119536906</v>
+        <v>119536881</v>
       </c>
       <c r="B99" t="n">
         <v>78526</v>
@@ -11602,10 +11607,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>539291</v>
+        <v>539513</v>
       </c>
       <c r="R99" t="n">
-        <v>7204141</v>
+        <v>7203718</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11637,7 +11642,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11647,7 +11652,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11674,10 +11679,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119536020</v>
+        <v>119536910</v>
       </c>
       <c r="B100" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11690,39 +11695,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>539508</v>
+        <v>539259</v>
       </c>
       <c r="R100" t="n">
-        <v>7203619</v>
+        <v>7203973</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13261,7 +13261,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119536891</v>
+        <v>119536889</v>
       </c>
       <c r="B114" t="n">
         <v>78526</v>
@@ -13301,10 +13301,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>539381</v>
+        <v>539408</v>
       </c>
       <c r="R114" t="n">
-        <v>7203929</v>
+        <v>7203874</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13346,7 +13346,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13373,7 +13373,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119536895</v>
+        <v>119536885</v>
       </c>
       <c r="B115" t="n">
         <v>78526</v>
@@ -13413,10 +13413,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>539355</v>
+        <v>539391</v>
       </c>
       <c r="R115" t="n">
-        <v>7203976</v>
+        <v>7203788</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -13448,7 +13448,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13485,10 +13485,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119536007</v>
+        <v>119536898</v>
       </c>
       <c r="B116" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13501,21 +13501,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13525,10 +13525,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>539248</v>
+        <v>539330</v>
       </c>
       <c r="R116" t="n">
-        <v>7203984</v>
+        <v>7204056</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13560,7 +13560,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13597,7 +13597,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119536889</v>
+        <v>119536907</v>
       </c>
       <c r="B117" t="n">
         <v>78526</v>
@@ -13637,10 +13637,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>539408</v>
+        <v>539291</v>
       </c>
       <c r="R117" t="n">
-        <v>7203874</v>
+        <v>7204060</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13682,7 +13682,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13709,7 +13709,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119536885</v>
+        <v>119536891</v>
       </c>
       <c r="B118" t="n">
         <v>78526</v>
@@ -13749,10 +13749,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>539391</v>
+        <v>539381</v>
       </c>
       <c r="R118" t="n">
-        <v>7203788</v>
+        <v>7203929</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13784,7 +13784,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13821,7 +13821,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119536898</v>
+        <v>119536895</v>
       </c>
       <c r="B119" t="n">
         <v>78526</v>
@@ -13861,10 +13861,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>539330</v>
+        <v>539355</v>
       </c>
       <c r="R119" t="n">
-        <v>7204056</v>
+        <v>7203976</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13906,7 +13906,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13933,10 +13933,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119536907</v>
+        <v>119536007</v>
       </c>
       <c r="B120" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13949,21 +13949,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13973,10 +13973,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>539291</v>
+        <v>539248</v>
       </c>
       <c r="R120" t="n">
-        <v>7204060</v>
+        <v>7203984</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -14008,7 +14008,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14269,10 +14269,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119537245</v>
+        <v>119536908</v>
       </c>
       <c r="B123" t="n">
-        <v>90957</v>
+        <v>78526</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14281,25 +14281,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14309,10 +14309,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>539319</v>
+        <v>539246</v>
       </c>
       <c r="R123" t="n">
-        <v>7204161</v>
+        <v>7203987</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14344,7 +14344,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14381,7 +14381,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119536915</v>
+        <v>119536888</v>
       </c>
       <c r="B124" t="n">
         <v>78526</v>
@@ -14421,10 +14421,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>539474</v>
+        <v>539404</v>
       </c>
       <c r="R124" t="n">
-        <v>7203605</v>
+        <v>7203854</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -14456,7 +14456,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14466,7 +14466,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14493,7 +14493,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119536908</v>
+        <v>119536876</v>
       </c>
       <c r="B125" t="n">
         <v>78526</v>
@@ -14533,10 +14533,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>539246</v>
+        <v>539520</v>
       </c>
       <c r="R125" t="n">
-        <v>7203987</v>
+        <v>7203615</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14568,7 +14568,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14578,7 +14578,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14605,10 +14605,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119536888</v>
+        <v>119536754</v>
       </c>
       <c r="B126" t="n">
-        <v>78526</v>
+        <v>56514</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14621,34 +14621,43 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>539404</v>
+        <v>539402</v>
       </c>
       <c r="R126" t="n">
-        <v>7203854</v>
+        <v>7203785</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14680,7 +14689,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14690,7 +14699,12 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Familjegrupp</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14717,10 +14731,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119536876</v>
+        <v>119537245</v>
       </c>
       <c r="B127" t="n">
-        <v>78526</v>
+        <v>90957</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14729,25 +14743,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14757,10 +14771,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>539520</v>
+        <v>539319</v>
       </c>
       <c r="R127" t="n">
-        <v>7203615</v>
+        <v>7204161</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14792,7 +14806,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14802,7 +14816,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14829,10 +14843,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119536754</v>
+        <v>119536915</v>
       </c>
       <c r="B128" t="n">
-        <v>56514</v>
+        <v>78526</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14845,43 +14859,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>539402</v>
+        <v>539474</v>
       </c>
       <c r="R128" t="n">
-        <v>7203785</v>
+        <v>7203605</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14913,7 +14918,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14923,12 +14928,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>17:02</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Familjegrupp</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16411,10 +16411,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119536913</v>
+        <v>119536331</v>
       </c>
       <c r="B142" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16427,21 +16427,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16451,10 +16451,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>539418</v>
+        <v>539389</v>
       </c>
       <c r="R142" t="n">
-        <v>7203718</v>
+        <v>7203819</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -16486,7 +16486,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16496,7 +16496,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16523,10 +16523,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119537248</v>
+        <v>119536334</v>
       </c>
       <c r="B143" t="n">
-        <v>77910</v>
+        <v>79608</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16539,21 +16539,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6437</v>
+        <v>2081</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16563,10 +16563,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>539311</v>
+        <v>539383</v>
       </c>
       <c r="R143" t="n">
-        <v>7203961</v>
+        <v>7203898</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16635,10 +16635,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119536680</v>
+        <v>119536913</v>
       </c>
       <c r="B144" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16647,25 +16647,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16675,10 +16675,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>539505</v>
+        <v>539418</v>
       </c>
       <c r="R144" t="n">
-        <v>7203636</v>
+        <v>7203718</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16747,10 +16747,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119536331</v>
+        <v>119537248</v>
       </c>
       <c r="B145" t="n">
-        <v>79608</v>
+        <v>77910</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16763,21 +16763,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2081</v>
+        <v>6437</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16787,10 +16787,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>539389</v>
+        <v>539311</v>
       </c>
       <c r="R145" t="n">
-        <v>7203819</v>
+        <v>7203961</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -16822,7 +16822,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16832,7 +16832,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16859,10 +16859,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119536334</v>
+        <v>119536680</v>
       </c>
       <c r="B146" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16871,25 +16871,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16899,10 +16899,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>539383</v>
+        <v>539505</v>
       </c>
       <c r="R146" t="n">
-        <v>7203898</v>
+        <v>7203636</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16944,7 +16944,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD146" t="b">

--- a/artfynd/A 28725-2024 artfynd.xlsx
+++ b/artfynd/A 28725-2024 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119535962</v>
+        <v>119536495</v>
       </c>
       <c r="B7" t="n">
-        <v>77473</v>
+        <v>90846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>314</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539520</v>
+        <v>539325</v>
       </c>
       <c r="R7" t="n">
-        <v>7203618</v>
+        <v>7204093</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536884</v>
+        <v>119536001</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539427</v>
+        <v>539342</v>
       </c>
       <c r="R8" t="n">
-        <v>7203760</v>
+        <v>7204082</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119536337</v>
+        <v>119536716</v>
       </c>
       <c r="B9" t="n">
-        <v>79608</v>
+        <v>80483</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539338</v>
+        <v>539315</v>
       </c>
       <c r="R9" t="n">
-        <v>7203941</v>
+        <v>7203955</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536345</v>
+        <v>119536485</v>
       </c>
       <c r="B10" t="n">
-        <v>79608</v>
+        <v>91005</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1533,25 +1533,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539411</v>
+        <v>539324</v>
       </c>
       <c r="R10" t="n">
-        <v>7203742</v>
+        <v>7204103</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536485</v>
+        <v>119536889</v>
       </c>
       <c r="B11" t="n">
-        <v>91005</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,25 +1645,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539324</v>
+        <v>539408</v>
       </c>
       <c r="R11" t="n">
-        <v>7204103</v>
+        <v>7203874</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119536882</v>
+        <v>119536892</v>
       </c>
       <c r="B12" t="n">
         <v>78526</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539508</v>
+        <v>539346</v>
       </c>
       <c r="R12" t="n">
-        <v>7203755</v>
+        <v>7203934</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119536712</v>
+        <v>119536893</v>
       </c>
       <c r="B13" t="n">
-        <v>90954</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,32 +1873,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539391</v>
+        <v>539338</v>
       </c>
       <c r="R13" t="n">
-        <v>7203790</v>
+        <v>7203941</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1930,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1940,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1951,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1968,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119536896</v>
+        <v>119536021</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,34 +1985,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539337</v>
+        <v>539499</v>
       </c>
       <c r="R14" t="n">
-        <v>7203986</v>
+        <v>7203671</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2043,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2053,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119536682</v>
+        <v>119536028</v>
       </c>
       <c r="B15" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2092,38 +2098,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539270</v>
+        <v>539414</v>
       </c>
       <c r="R15" t="n">
-        <v>7204025</v>
+        <v>7203683</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2155,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2165,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119537127</v>
+        <v>119537029</v>
       </c>
       <c r="B16" t="n">
-        <v>79642</v>
+        <v>82305</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,25 +2215,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2232,10 +2243,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>539441</v>
+        <v>539525</v>
       </c>
       <c r="R16" t="n">
-        <v>7203738</v>
+        <v>7203612</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2267,7 +2278,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2277,7 +2288,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2304,10 +2315,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119536342</v>
+        <v>119536910</v>
       </c>
       <c r="B17" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2320,21 +2331,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2416,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119536554</v>
+        <v>119536683</v>
       </c>
       <c r="B18" t="n">
-        <v>90916</v>
+        <v>79643</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2428,25 +2439,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1506</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2456,10 +2467,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>539431</v>
+        <v>539259</v>
       </c>
       <c r="R18" t="n">
-        <v>7203761</v>
+        <v>7203973</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2491,7 +2502,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2501,7 +2512,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,10 +2539,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119536718</v>
+        <v>119536684</v>
       </c>
       <c r="B19" t="n">
-        <v>79567</v>
+        <v>79643</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2544,21 +2555,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2568,10 +2579,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>539353</v>
+        <v>539409</v>
       </c>
       <c r="R19" t="n">
-        <v>7203941</v>
+        <v>7203733</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2603,7 +2614,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2613,7 +2624,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2640,10 +2651,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536784</v>
+        <v>119536898</v>
       </c>
       <c r="B20" t="n">
-        <v>97806</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2652,25 +2663,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219795</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2680,10 +2691,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>539347</v>
+        <v>539330</v>
       </c>
       <c r="R20" t="n">
-        <v>7203938</v>
+        <v>7204056</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2715,7 +2726,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2725,7 +2736,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2752,10 +2763,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119536339</v>
+        <v>119536790</v>
       </c>
       <c r="B21" t="n">
-        <v>79608</v>
+        <v>90576</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2768,21 +2779,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2792,10 +2803,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>539330</v>
+        <v>539492</v>
       </c>
       <c r="R21" t="n">
-        <v>7204058</v>
+        <v>7203590</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2827,7 +2838,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2837,7 +2848,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2864,10 +2875,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536790</v>
+        <v>119535962</v>
       </c>
       <c r="B22" t="n">
-        <v>90576</v>
+        <v>77473</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2880,21 +2891,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2904,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>539492</v>
+        <v>539520</v>
       </c>
       <c r="R22" t="n">
-        <v>7203590</v>
+        <v>7203618</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2939,7 +2950,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2949,7 +2960,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2976,10 +2987,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119535983</v>
+        <v>119536685</v>
       </c>
       <c r="B23" t="n">
-        <v>90527</v>
+        <v>79643</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2992,21 +3003,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3016,10 +3027,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>539249</v>
+        <v>539419</v>
       </c>
       <c r="R23" t="n">
-        <v>7203985</v>
+        <v>7203720</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3051,7 +3062,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3061,7 +3072,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3088,10 +3099,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119536619</v>
+        <v>119535969</v>
       </c>
       <c r="B24" t="n">
-        <v>94311</v>
+        <v>74638</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3100,25 +3111,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3128,10 +3139,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>539501</v>
+        <v>539512</v>
       </c>
       <c r="R24" t="n">
-        <v>7203654</v>
+        <v>7203549</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3163,7 +3174,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3173,7 +3184,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3200,10 +3211,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119536327</v>
+        <v>119537248</v>
       </c>
       <c r="B25" t="n">
-        <v>79608</v>
+        <v>77910</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3216,21 +3227,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6437</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3240,10 +3251,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>539506</v>
+        <v>539311</v>
       </c>
       <c r="R25" t="n">
-        <v>7203636</v>
+        <v>7203961</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3275,7 +3286,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3285,7 +3296,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3312,10 +3323,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119536777</v>
+        <v>119536879</v>
       </c>
       <c r="B26" t="n">
-        <v>74622</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3324,25 +3335,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3352,10 +3363,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>539510</v>
+        <v>539500</v>
       </c>
       <c r="R26" t="n">
-        <v>7203622</v>
+        <v>7203672</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3387,7 +3398,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3397,7 +3408,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3424,10 +3435,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119535969</v>
+        <v>119536880</v>
       </c>
       <c r="B27" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3440,21 +3451,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3464,10 +3475,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>539512</v>
+        <v>539505</v>
       </c>
       <c r="R27" t="n">
-        <v>7203549</v>
+        <v>7203692</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3499,7 +3510,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3509,7 +3520,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3536,10 +3547,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119537149</v>
+        <v>119536904</v>
       </c>
       <c r="B28" t="n">
-        <v>77458</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3552,21 +3563,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3576,10 +3587,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>539312</v>
+        <v>539309</v>
       </c>
       <c r="R28" t="n">
-        <v>7203957</v>
+        <v>7204157</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3611,7 +3622,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3621,7 +3632,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3648,10 +3659,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119537128</v>
+        <v>119536764</v>
       </c>
       <c r="B29" t="n">
-        <v>79642</v>
+        <v>90558</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3660,25 +3671,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3688,10 +3699,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>539389</v>
+        <v>539508</v>
       </c>
       <c r="R29" t="n">
-        <v>7203822</v>
+        <v>7203557</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3723,7 +3734,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3733,7 +3744,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3760,10 +3771,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119536273</v>
+        <v>119536330</v>
       </c>
       <c r="B30" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3772,25 +3783,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3800,10 +3811,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>539392</v>
+        <v>539440</v>
       </c>
       <c r="R30" t="n">
-        <v>7203821</v>
+        <v>7203741</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3835,7 +3846,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3845,7 +3856,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3872,10 +3883,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119536005</v>
+        <v>119536805</v>
       </c>
       <c r="B31" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3888,21 +3899,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3912,10 +3923,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>539315</v>
+        <v>539529</v>
       </c>
       <c r="R31" t="n">
-        <v>7204159</v>
+        <v>7203613</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3947,7 +3958,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3957,7 +3968,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3984,10 +3995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119536871</v>
+        <v>119536025</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4000,34 +4011,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>539512</v>
+        <v>539346</v>
       </c>
       <c r="R32" t="n">
-        <v>7203548</v>
+        <v>7203957</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4059,7 +4075,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4069,7 +4085,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4096,10 +4112,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119536328</v>
+        <v>119536026</v>
       </c>
       <c r="B33" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4112,34 +4128,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>539505</v>
+        <v>539337</v>
       </c>
       <c r="R33" t="n">
-        <v>7203689</v>
+        <v>7203986</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4171,7 +4192,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4181,7 +4202,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4208,10 +4229,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119536028</v>
+        <v>119536712</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>90954</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4224,39 +4245,32 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>539414</v>
+        <v>539391</v>
       </c>
       <c r="R34" t="n">
-        <v>7203683</v>
+        <v>7203790</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4288,7 +4302,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4298,7 +4312,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4307,6 +4321,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4325,7 +4340,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536348</v>
+        <v>119536342</v>
       </c>
       <c r="B35" t="n">
         <v>79608</v>
@@ -4365,10 +4380,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>539466</v>
+        <v>539259</v>
       </c>
       <c r="R35" t="n">
-        <v>7203618</v>
+        <v>7203973</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4400,7 +4415,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4410,7 +4425,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4437,7 +4452,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536332</v>
+        <v>119536344</v>
       </c>
       <c r="B36" t="n">
         <v>79608</v>
@@ -4477,10 +4492,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>539404</v>
+        <v>539392</v>
       </c>
       <c r="R36" t="n">
-        <v>7203853</v>
+        <v>7203749</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4512,7 +4527,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4522,7 +4537,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4549,7 +4564,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119536330</v>
+        <v>119536327</v>
       </c>
       <c r="B37" t="n">
         <v>79608</v>
@@ -4589,10 +4604,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>539440</v>
+        <v>539506</v>
       </c>
       <c r="R37" t="n">
-        <v>7203741</v>
+        <v>7203636</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4624,7 +4639,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4634,7 +4649,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4661,10 +4676,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119536893</v>
+        <v>119536681</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4673,25 +4688,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4701,10 +4716,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539338</v>
+        <v>539381</v>
       </c>
       <c r="R38" t="n">
-        <v>7203941</v>
+        <v>7203902</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4736,7 +4751,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4746,7 +4761,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4773,10 +4788,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119536683</v>
+        <v>119536406</v>
       </c>
       <c r="B39" t="n">
-        <v>79643</v>
+        <v>79511</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4789,21 +4804,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4813,10 +4828,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539259</v>
+        <v>539285</v>
       </c>
       <c r="R39" t="n">
-        <v>7203973</v>
+        <v>7203971</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4848,7 +4863,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4858,7 +4873,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4885,10 +4900,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119536405</v>
+        <v>119537130</v>
       </c>
       <c r="B40" t="n">
-        <v>79511</v>
+        <v>79642</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4901,21 +4916,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4925,10 +4940,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539273</v>
+        <v>539259</v>
       </c>
       <c r="R40" t="n">
-        <v>7203974</v>
+        <v>7203973</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4960,7 +4975,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4970,7 +4985,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4997,10 +5012,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119536645</v>
+        <v>119536894</v>
       </c>
       <c r="B41" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5013,21 +5028,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5037,10 +5052,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>539289</v>
+        <v>539344</v>
       </c>
       <c r="R41" t="n">
-        <v>7204141</v>
+        <v>7203950</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5072,7 +5087,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5082,7 +5097,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5109,10 +5124,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119537029</v>
+        <v>119536876</v>
       </c>
       <c r="B42" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5125,21 +5140,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5149,10 +5164,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>539525</v>
+        <v>539520</v>
       </c>
       <c r="R42" t="n">
-        <v>7203612</v>
+        <v>7203615</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5184,7 +5199,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5194,7 +5209,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5221,10 +5236,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119536003</v>
+        <v>119536718</v>
       </c>
       <c r="B43" t="n">
-        <v>90562</v>
+        <v>79567</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5233,25 +5248,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5261,10 +5276,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>539322</v>
+        <v>539353</v>
       </c>
       <c r="R43" t="n">
-        <v>7204109</v>
+        <v>7203941</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5296,7 +5311,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5306,7 +5321,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5333,10 +5348,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119536096</v>
+        <v>119537245</v>
       </c>
       <c r="B44" t="n">
-        <v>56522</v>
+        <v>90957</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5349,38 +5364,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>4217</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>539506</v>
+        <v>539319</v>
       </c>
       <c r="R44" t="n">
-        <v>7203636</v>
+        <v>7204161</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5412,7 +5423,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5422,7 +5433,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5449,10 +5460,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119536681</v>
+        <v>119537131</v>
       </c>
       <c r="B45" t="n">
-        <v>79643</v>
+        <v>79642</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5465,21 +5476,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5489,10 +5500,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>539381</v>
+        <v>539417</v>
       </c>
       <c r="R45" t="n">
-        <v>7203902</v>
+        <v>7203723</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5524,7 +5535,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5534,7 +5545,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5561,10 +5572,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119536343</v>
+        <v>119536884</v>
       </c>
       <c r="B46" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5577,21 +5588,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5601,10 +5612,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>539360</v>
+        <v>539427</v>
       </c>
       <c r="R46" t="n">
-        <v>7203797</v>
+        <v>7203760</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5636,7 +5647,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5646,7 +5657,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5673,10 +5684,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119536403</v>
+        <v>119536891</v>
       </c>
       <c r="B47" t="n">
-        <v>94323</v>
+        <v>78526</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5685,25 +5696,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5713,10 +5724,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>539514</v>
+        <v>539381</v>
       </c>
       <c r="R47" t="n">
-        <v>7203744</v>
+        <v>7203929</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5748,7 +5759,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5758,7 +5769,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5785,10 +5796,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119536901</v>
+        <v>119536645</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5801,21 +5812,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5825,10 +5836,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>539322</v>
+        <v>539289</v>
       </c>
       <c r="R48" t="n">
-        <v>7204109</v>
+        <v>7204141</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5860,7 +5871,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5870,7 +5881,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5897,10 +5908,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119536347</v>
+        <v>119536717</v>
       </c>
       <c r="B49" t="n">
-        <v>79608</v>
+        <v>80483</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5913,21 +5924,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>1049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5937,10 +5948,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>539474</v>
+        <v>539314</v>
       </c>
       <c r="R49" t="n">
-        <v>7203607</v>
+        <v>7203905</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5972,7 +5983,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5982,7 +5993,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6009,7 +6020,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119536335</v>
+        <v>119536328</v>
       </c>
       <c r="B50" t="n">
         <v>79608</v>
@@ -6049,10 +6060,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>539371</v>
+        <v>539505</v>
       </c>
       <c r="R50" t="n">
-        <v>7203932</v>
+        <v>7203689</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6084,7 +6095,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6094,7 +6105,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6121,10 +6132,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119536329</v>
+        <v>119536000</v>
       </c>
       <c r="B51" t="n">
-        <v>79608</v>
+        <v>90905</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6133,25 +6144,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>2062</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6161,10 +6172,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>539508</v>
+        <v>539319</v>
       </c>
       <c r="R51" t="n">
-        <v>7203755</v>
+        <v>7204161</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6196,7 +6207,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6206,7 +6217,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Troligen S. Delicata</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6217,6 +6233,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6233,10 +6264,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119536401</v>
+        <v>119536347</v>
       </c>
       <c r="B52" t="n">
-        <v>99161</v>
+        <v>79608</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6245,25 +6276,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6273,10 +6304,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>539522</v>
+        <v>539474</v>
       </c>
       <c r="R52" t="n">
-        <v>7203617</v>
+        <v>7203607</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6308,7 +6339,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6318,7 +6349,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6345,10 +6376,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119536274</v>
+        <v>119536329</v>
       </c>
       <c r="B53" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6357,25 +6388,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6385,10 +6416,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>539353</v>
+        <v>539508</v>
       </c>
       <c r="R53" t="n">
-        <v>7203981</v>
+        <v>7203755</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6420,7 +6451,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6430,7 +6461,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6457,10 +6488,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119536275</v>
+        <v>119535983</v>
       </c>
       <c r="B54" t="n">
-        <v>79636</v>
+        <v>90527</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6473,21 +6504,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6497,10 +6528,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>539330</v>
+        <v>539249</v>
       </c>
       <c r="R54" t="n">
-        <v>7204059</v>
+        <v>7203985</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6532,7 +6563,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6542,7 +6573,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6569,10 +6600,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119536026</v>
+        <v>119537048</v>
       </c>
       <c r="B55" t="n">
-        <v>57310</v>
+        <v>90043</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6585,39 +6616,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>3286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>539337</v>
+        <v>539427</v>
       </c>
       <c r="R55" t="n">
-        <v>7203986</v>
+        <v>7203770</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6649,7 +6675,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6659,7 +6685,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6686,10 +6712,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119535949</v>
+        <v>119537129</v>
       </c>
       <c r="B56" t="n">
-        <v>104994</v>
+        <v>79642</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6702,21 +6728,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221725</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6726,10 +6752,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539400</v>
+        <v>539380</v>
       </c>
       <c r="R56" t="n">
-        <v>7203837</v>
+        <v>7203902</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6761,7 +6787,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6771,7 +6797,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6798,10 +6824,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119536520</v>
+        <v>119536269</v>
       </c>
       <c r="B57" t="n">
-        <v>96862</v>
+        <v>79636</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6814,21 +6840,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6838,10 +6864,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539260</v>
+        <v>539518</v>
       </c>
       <c r="R57" t="n">
-        <v>7203982</v>
+        <v>7203548</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6873,7 +6899,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6883,7 +6909,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6910,10 +6936,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119536340</v>
+        <v>119536906</v>
       </c>
       <c r="B58" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6926,21 +6952,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6950,10 +6976,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>539325</v>
+        <v>539291</v>
       </c>
       <c r="R58" t="n">
-        <v>7204093</v>
+        <v>7204141</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6985,7 +7011,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6995,7 +7021,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7022,10 +7048,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119537048</v>
+        <v>119536007</v>
       </c>
       <c r="B59" t="n">
-        <v>90043</v>
+        <v>90562</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7038,21 +7064,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3286</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7062,10 +7088,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>539427</v>
+        <v>539248</v>
       </c>
       <c r="R59" t="n">
-        <v>7203770</v>
+        <v>7203984</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7097,7 +7123,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7107,7 +7133,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7134,10 +7160,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119536717</v>
+        <v>119536680</v>
       </c>
       <c r="B60" t="n">
-        <v>80483</v>
+        <v>79643</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7146,25 +7172,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1049</v>
+        <v>6464</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7174,10 +7200,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>539314</v>
+        <v>539505</v>
       </c>
       <c r="R60" t="n">
-        <v>7203905</v>
+        <v>7203636</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7209,7 +7235,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7219,7 +7245,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7246,7 +7272,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119536874</v>
+        <v>119536900</v>
       </c>
       <c r="B61" t="n">
         <v>78526</v>
@@ -7286,10 +7312,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>539525</v>
+        <v>539326</v>
       </c>
       <c r="R61" t="n">
-        <v>7203611</v>
+        <v>7204101</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7321,7 +7347,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7331,7 +7357,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7358,7 +7384,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119536900</v>
+        <v>119536885</v>
       </c>
       <c r="B62" t="n">
         <v>78526</v>
@@ -7398,10 +7424,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>539326</v>
+        <v>539391</v>
       </c>
       <c r="R62" t="n">
-        <v>7204101</v>
+        <v>7203788</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7433,7 +7459,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7443,7 +7469,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7470,10 +7496,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119537126</v>
+        <v>119536911</v>
       </c>
       <c r="B63" t="n">
-        <v>79642</v>
+        <v>78526</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7482,20 +7508,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7510,10 +7536,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>539504</v>
+        <v>539314</v>
       </c>
       <c r="R63" t="n">
-        <v>7203691</v>
+        <v>7203905</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7545,7 +7571,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7555,7 +7581,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7582,10 +7608,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119536269</v>
+        <v>119536005</v>
       </c>
       <c r="B64" t="n">
-        <v>79636</v>
+        <v>90562</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7594,25 +7620,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7622,10 +7648,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>539518</v>
+        <v>539315</v>
       </c>
       <c r="R64" t="n">
-        <v>7203548</v>
+        <v>7204159</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7657,7 +7683,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7667,7 +7693,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7694,10 +7720,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119536805</v>
+        <v>119537149</v>
       </c>
       <c r="B65" t="n">
-        <v>90580</v>
+        <v>77458</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7710,21 +7736,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6487</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7734,10 +7760,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>539529</v>
+        <v>539312</v>
       </c>
       <c r="R65" t="n">
-        <v>7203613</v>
+        <v>7203957</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7769,7 +7795,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7779,7 +7805,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7806,10 +7832,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119536004</v>
+        <v>119536890</v>
       </c>
       <c r="B66" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7822,21 +7848,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7846,10 +7872,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>539306</v>
+        <v>539381</v>
       </c>
       <c r="R66" t="n">
-        <v>7204149</v>
+        <v>7203909</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7881,7 +7907,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7891,7 +7917,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7918,10 +7944,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119535950</v>
+        <v>119536274</v>
       </c>
       <c r="B67" t="n">
-        <v>104994</v>
+        <v>79636</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7934,21 +7960,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7958,10 +7984,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>539261</v>
+        <v>539353</v>
       </c>
       <c r="R67" t="n">
-        <v>7203983</v>
+        <v>7203981</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7993,7 +8019,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8003,7 +8029,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8030,10 +8056,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119537129</v>
+        <v>119536784</v>
       </c>
       <c r="B68" t="n">
-        <v>79642</v>
+        <v>97806</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8046,21 +8072,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6463</v>
+        <v>219795</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8070,10 +8096,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>539380</v>
+        <v>539347</v>
       </c>
       <c r="R68" t="n">
-        <v>7203902</v>
+        <v>7203938</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8105,7 +8131,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8115,7 +8141,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8142,10 +8168,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119536002</v>
+        <v>119536346</v>
       </c>
       <c r="B69" t="n">
-        <v>90562</v>
+        <v>79608</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8158,21 +8184,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8182,10 +8208,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>539326</v>
+        <v>539419</v>
       </c>
       <c r="R69" t="n">
-        <v>7204093</v>
+        <v>7203720</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8217,7 +8243,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8227,7 +8253,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8254,10 +8280,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119536904</v>
+        <v>119536336</v>
       </c>
       <c r="B70" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8270,21 +8296,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8294,10 +8320,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>539309</v>
+        <v>539352</v>
       </c>
       <c r="R70" t="n">
-        <v>7204157</v>
+        <v>7203941</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8329,7 +8355,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8339,7 +8365,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8366,10 +8392,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119536879</v>
+        <v>119536341</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8382,21 +8408,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8406,10 +8432,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>539500</v>
+        <v>539268</v>
       </c>
       <c r="R71" t="n">
-        <v>7203672</v>
+        <v>7204021</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8441,7 +8467,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8451,7 +8477,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8478,10 +8504,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119536892</v>
+        <v>119537127</v>
       </c>
       <c r="B72" t="n">
-        <v>78526</v>
+        <v>79642</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8490,20 +8516,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8518,10 +8544,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>539346</v>
+        <v>539441</v>
       </c>
       <c r="R72" t="n">
-        <v>7203934</v>
+        <v>7203738</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8553,7 +8579,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8563,7 +8589,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8590,10 +8616,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119536875</v>
+        <v>119537126</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>79642</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8602,20 +8628,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8630,10 +8656,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>539503</v>
+        <v>539504</v>
       </c>
       <c r="R73" t="n">
-        <v>7203619</v>
+        <v>7203691</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8665,7 +8691,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8675,7 +8701,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8702,10 +8728,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119537112</v>
+        <v>119536024</v>
       </c>
       <c r="B74" t="n">
-        <v>91128</v>
+        <v>57310</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8714,38 +8740,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>539486</v>
+        <v>539515</v>
       </c>
       <c r="R74" t="n">
-        <v>7203594</v>
+        <v>7203720</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8777,7 +8808,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8787,7 +8818,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8814,10 +8845,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119536806</v>
+        <v>119536097</v>
       </c>
       <c r="B75" t="n">
-        <v>90580</v>
+        <v>56522</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8826,38 +8857,54 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>539337</v>
+        <v>539309</v>
       </c>
       <c r="R75" t="n">
-        <v>7204110</v>
+        <v>7204157</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8889,7 +8936,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8899,7 +8946,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8926,10 +8973,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119536344</v>
+        <v>119535950</v>
       </c>
       <c r="B76" t="n">
-        <v>79608</v>
+        <v>104994</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8938,25 +8985,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>221725</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8966,10 +9013,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>539392</v>
+        <v>539261</v>
       </c>
       <c r="R76" t="n">
-        <v>7203749</v>
+        <v>7203983</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9001,7 +9048,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9011,7 +9058,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9038,10 +9085,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119536873</v>
+        <v>119537128</v>
       </c>
       <c r="B77" t="n">
-        <v>78526</v>
+        <v>79642</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9050,20 +9097,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9078,10 +9125,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>539528</v>
+        <v>539389</v>
       </c>
       <c r="R77" t="n">
-        <v>7203612</v>
+        <v>7203822</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9113,7 +9160,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9123,7 +9170,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9150,7 +9197,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119536883</v>
+        <v>119536886</v>
       </c>
       <c r="B78" t="n">
         <v>78526</v>
@@ -9190,10 +9237,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>539438</v>
+        <v>539387</v>
       </c>
       <c r="R78" t="n">
-        <v>7203740</v>
+        <v>7203818</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9225,7 +9272,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9235,7 +9282,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9262,10 +9309,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119537130</v>
+        <v>119536912</v>
       </c>
       <c r="B79" t="n">
-        <v>79642</v>
+        <v>78526</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9274,20 +9321,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -9302,10 +9349,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>539259</v>
+        <v>539412</v>
       </c>
       <c r="R79" t="n">
-        <v>7203973</v>
+        <v>7203743</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9337,7 +9384,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9347,7 +9394,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9374,7 +9421,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119536887</v>
+        <v>119536908</v>
       </c>
       <c r="B80" t="n">
         <v>78526</v>
@@ -9414,10 +9461,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>539398</v>
+        <v>539246</v>
       </c>
       <c r="R80" t="n">
-        <v>7203841</v>
+        <v>7203987</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9449,7 +9496,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9459,7 +9506,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9486,10 +9533,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119536890</v>
+        <v>119536334</v>
       </c>
       <c r="B81" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9502,21 +9549,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9526,10 +9573,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>539381</v>
+        <v>539383</v>
       </c>
       <c r="R81" t="n">
-        <v>7203909</v>
+        <v>7203898</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9561,7 +9608,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9571,7 +9618,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9598,10 +9645,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119536024</v>
+        <v>119536554</v>
       </c>
       <c r="B82" t="n">
-        <v>57310</v>
+        <v>90916</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9610,43 +9657,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>539515</v>
+        <v>539431</v>
       </c>
       <c r="R82" t="n">
-        <v>7203720</v>
+        <v>7203761</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9678,7 +9720,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9688,7 +9730,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9715,10 +9757,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119536097</v>
+        <v>119536401</v>
       </c>
       <c r="B83" t="n">
-        <v>56522</v>
+        <v>99161</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9731,50 +9773,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>2082</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>539309</v>
+        <v>539522</v>
       </c>
       <c r="R83" t="n">
-        <v>7204157</v>
+        <v>7203617</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9806,7 +9832,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9816,7 +9842,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9843,10 +9869,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119536000</v>
+        <v>119537142</v>
       </c>
       <c r="B84" t="n">
-        <v>90905</v>
+        <v>74630</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9855,25 +9881,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2062</v>
+        <v>308</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9883,10 +9909,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>539319</v>
+        <v>539514</v>
       </c>
       <c r="R84" t="n">
-        <v>7204161</v>
+        <v>7203719</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9918,7 +9944,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9928,12 +9954,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Troligen S. Delicata</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9944,21 +9965,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -9975,10 +9981,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119536897</v>
+        <v>119536493</v>
       </c>
       <c r="B85" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9991,21 +9997,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10015,10 +10021,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>539335</v>
+        <v>539429</v>
       </c>
       <c r="R85" t="n">
-        <v>7204015</v>
+        <v>7203761</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10050,7 +10056,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10060,7 +10066,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10087,10 +10093,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119536870</v>
+        <v>119536777</v>
       </c>
       <c r="B86" t="n">
-        <v>78526</v>
+        <v>74622</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10099,25 +10105,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10127,10 +10133,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>539517</v>
+        <v>539510</v>
       </c>
       <c r="R86" t="n">
-        <v>7203551</v>
+        <v>7203622</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10162,7 +10168,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10172,7 +10178,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10199,10 +10205,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119536406</v>
+        <v>119536754</v>
       </c>
       <c r="B87" t="n">
-        <v>79511</v>
+        <v>56514</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10211,38 +10217,47 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6456</v>
+        <v>102612</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>539285</v>
+        <v>539402</v>
       </c>
       <c r="R87" t="n">
-        <v>7203971</v>
+        <v>7203785</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10274,7 +10289,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10284,7 +10299,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Familjegrupp</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10311,10 +10331,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119536878</v>
+        <v>119536337</v>
       </c>
       <c r="B88" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10327,21 +10347,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10351,10 +10371,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>539504</v>
+        <v>539338</v>
       </c>
       <c r="R88" t="n">
-        <v>7203658</v>
+        <v>7203941</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10386,7 +10406,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10396,7 +10416,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10423,7 +10443,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119536341</v>
+        <v>119536338</v>
       </c>
       <c r="B89" t="n">
         <v>79608</v>
@@ -10463,10 +10483,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>539268</v>
+        <v>539333</v>
       </c>
       <c r="R89" t="n">
-        <v>7204021</v>
+        <v>7204016</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10498,7 +10518,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10508,7 +10528,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10535,10 +10555,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119536493</v>
+        <v>119536332</v>
       </c>
       <c r="B90" t="n">
-        <v>90846</v>
+        <v>79608</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10551,21 +10571,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10575,10 +10595,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>539429</v>
+        <v>539404</v>
       </c>
       <c r="R90" t="n">
-        <v>7203761</v>
+        <v>7203853</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10610,7 +10630,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10620,7 +10640,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10647,7 +10667,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119536899</v>
+        <v>119536903</v>
       </c>
       <c r="B91" t="n">
         <v>78526</v>
@@ -10687,10 +10707,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>539342</v>
+        <v>539306</v>
       </c>
       <c r="R91" t="n">
-        <v>7204082</v>
+        <v>7204148</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10722,7 +10742,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10732,7 +10752,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10759,10 +10779,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119536107</v>
+        <v>119536873</v>
       </c>
       <c r="B92" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10775,43 +10795,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>539353</v>
+        <v>539528</v>
       </c>
       <c r="R92" t="n">
-        <v>7203941</v>
+        <v>7203612</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10843,7 +10854,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10853,7 +10864,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10880,10 +10891,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119536764</v>
+        <v>119536870</v>
       </c>
       <c r="B93" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10896,21 +10907,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10920,10 +10931,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>539508</v>
+        <v>539517</v>
       </c>
       <c r="R93" t="n">
-        <v>7203557</v>
+        <v>7203551</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10955,7 +10966,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10965,7 +10976,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10992,10 +11003,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119536021</v>
+        <v>119536874</v>
       </c>
       <c r="B94" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11008,39 +11019,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>539499</v>
+        <v>539525</v>
       </c>
       <c r="R94" t="n">
-        <v>7203671</v>
+        <v>7203611</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11072,7 +11078,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11082,7 +11088,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11109,10 +11115,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119536025</v>
+        <v>119536881</v>
       </c>
       <c r="B95" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11125,39 +11131,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>539346</v>
+        <v>539513</v>
       </c>
       <c r="R95" t="n">
-        <v>7203957</v>
+        <v>7203718</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11189,7 +11190,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11199,7 +11200,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11226,10 +11227,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119536020</v>
+        <v>119536275</v>
       </c>
       <c r="B96" t="n">
-        <v>57310</v>
+        <v>79636</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11238,43 +11239,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>539508</v>
+        <v>539330</v>
       </c>
       <c r="R96" t="n">
-        <v>7203619</v>
+        <v>7204059</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11306,7 +11302,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11316,7 +11312,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11343,7 +11339,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119536880</v>
+        <v>119536914</v>
       </c>
       <c r="B97" t="n">
         <v>78526</v>
@@ -11383,10 +11379,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>539505</v>
+        <v>539438</v>
       </c>
       <c r="R97" t="n">
-        <v>7203692</v>
+        <v>7203711</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11418,7 +11414,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11428,7 +11424,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11455,7 +11451,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119536906</v>
+        <v>119536877</v>
       </c>
       <c r="B98" t="n">
         <v>78526</v>
@@ -11495,10 +11491,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>539291</v>
+        <v>539504</v>
       </c>
       <c r="R98" t="n">
-        <v>7204141</v>
+        <v>7203633</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11530,7 +11526,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11540,7 +11536,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11567,7 +11563,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119536881</v>
+        <v>119536915</v>
       </c>
       <c r="B99" t="n">
         <v>78526</v>
@@ -11607,10 +11603,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>539513</v>
+        <v>539474</v>
       </c>
       <c r="R99" t="n">
-        <v>7203718</v>
+        <v>7203605</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11642,7 +11638,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11652,7 +11648,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11679,7 +11675,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119536910</v>
+        <v>119536878</v>
       </c>
       <c r="B100" t="n">
         <v>78526</v>
@@ -11719,10 +11715,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>539259</v>
+        <v>539504</v>
       </c>
       <c r="R100" t="n">
-        <v>7203973</v>
+        <v>7203658</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11754,7 +11750,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11764,7 +11760,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11791,10 +11787,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119536707</v>
+        <v>119536003</v>
       </c>
       <c r="B101" t="n">
-        <v>57421</v>
+        <v>90562</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11803,47 +11799,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>539474</v>
+        <v>539322</v>
       </c>
       <c r="R101" t="n">
-        <v>7203674</v>
+        <v>7204109</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11875,7 +11862,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11885,7 +11872,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11912,10 +11899,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119536912</v>
+        <v>119536343</v>
       </c>
       <c r="B102" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11928,21 +11915,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11952,10 +11939,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>539412</v>
+        <v>539360</v>
       </c>
       <c r="R102" t="n">
-        <v>7203743</v>
+        <v>7203797</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11987,7 +11974,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11997,7 +11984,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12024,10 +12011,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119536877</v>
+        <v>119536405</v>
       </c>
       <c r="B103" t="n">
-        <v>78526</v>
+        <v>79511</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12036,25 +12023,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12064,10 +12051,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>539504</v>
+        <v>539273</v>
       </c>
       <c r="R103" t="n">
-        <v>7203633</v>
+        <v>7203974</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12099,7 +12086,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12109,7 +12096,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12136,10 +12123,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119537131</v>
+        <v>119536882</v>
       </c>
       <c r="B104" t="n">
-        <v>79642</v>
+        <v>78526</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12148,20 +12135,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -12176,10 +12163,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>539417</v>
+        <v>539508</v>
       </c>
       <c r="R104" t="n">
-        <v>7203723</v>
+        <v>7203755</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12211,7 +12198,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12221,7 +12208,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12248,10 +12235,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119536270</v>
+        <v>119536913</v>
       </c>
       <c r="B105" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12260,25 +12247,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12288,10 +12275,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>539441</v>
+        <v>539418</v>
       </c>
       <c r="R105" t="n">
-        <v>7203738</v>
+        <v>7203718</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12323,7 +12310,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12333,7 +12320,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12360,10 +12347,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119536276</v>
+        <v>119536902</v>
       </c>
       <c r="B106" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12372,25 +12359,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12400,10 +12387,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>539490</v>
+        <v>539340</v>
       </c>
       <c r="R106" t="n">
-        <v>7203595</v>
+        <v>7204108</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12435,7 +12422,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12445,7 +12432,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12472,10 +12459,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119536027</v>
+        <v>119536004</v>
       </c>
       <c r="B107" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12488,39 +12475,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>539326</v>
+        <v>539306</v>
       </c>
       <c r="R107" t="n">
-        <v>7204100</v>
+        <v>7204149</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12552,7 +12534,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12562,7 +12544,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12589,10 +12571,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119536909</v>
+        <v>119536002</v>
       </c>
       <c r="B108" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12605,21 +12587,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12629,10 +12611,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>539260</v>
+        <v>539326</v>
       </c>
       <c r="R108" t="n">
-        <v>7203982</v>
+        <v>7204093</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12664,7 +12646,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12674,7 +12656,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12701,10 +12683,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119536483</v>
+        <v>119536619</v>
       </c>
       <c r="B109" t="n">
-        <v>91005</v>
+        <v>94311</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12713,25 +12695,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1209</v>
+        <v>2809</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12741,10 +12723,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>539427</v>
+        <v>539501</v>
       </c>
       <c r="R109" t="n">
-        <v>7203755</v>
+        <v>7203654</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12776,7 +12758,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12786,7 +12768,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12813,10 +12795,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119536495</v>
+        <v>119536345</v>
       </c>
       <c r="B110" t="n">
-        <v>90846</v>
+        <v>79608</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12829,21 +12811,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12853,10 +12835,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>539325</v>
+        <v>539411</v>
       </c>
       <c r="R110" t="n">
-        <v>7204093</v>
+        <v>7203742</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12888,7 +12870,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12898,7 +12880,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12925,10 +12907,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119536886</v>
+        <v>119536339</v>
       </c>
       <c r="B111" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12941,21 +12923,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12965,10 +12947,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>539387</v>
+        <v>539330</v>
       </c>
       <c r="R111" t="n">
-        <v>7203818</v>
+        <v>7204058</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -13000,7 +12982,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13010,7 +12992,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13037,10 +13019,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119536902</v>
+        <v>119536806</v>
       </c>
       <c r="B112" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13053,21 +13035,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13077,10 +13059,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>539340</v>
+        <v>539337</v>
       </c>
       <c r="R112" t="n">
-        <v>7204108</v>
+        <v>7204110</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -13112,7 +13094,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13122,7 +13104,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13149,10 +13131,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119537142</v>
+        <v>119536887</v>
       </c>
       <c r="B113" t="n">
-        <v>74630</v>
+        <v>78526</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13165,21 +13147,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13189,10 +13171,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>539514</v>
+        <v>539398</v>
       </c>
       <c r="R113" t="n">
-        <v>7203719</v>
+        <v>7203841</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -13224,7 +13206,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13234,7 +13216,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13261,7 +13243,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119536889</v>
+        <v>119536907</v>
       </c>
       <c r="B114" t="n">
         <v>78526</v>
@@ -13301,10 +13283,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>539408</v>
+        <v>539291</v>
       </c>
       <c r="R114" t="n">
-        <v>7203874</v>
+        <v>7204060</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -13336,7 +13318,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13346,7 +13328,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13373,7 +13355,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119536885</v>
+        <v>119536905</v>
       </c>
       <c r="B115" t="n">
         <v>78526</v>
@@ -13413,10 +13395,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>539391</v>
+        <v>539319</v>
       </c>
       <c r="R115" t="n">
-        <v>7203788</v>
+        <v>7204163</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -13448,7 +13430,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13458,7 +13440,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13485,7 +13467,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119536898</v>
+        <v>119536909</v>
       </c>
       <c r="B116" t="n">
         <v>78526</v>
@@ -13525,10 +13507,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>539330</v>
+        <v>539260</v>
       </c>
       <c r="R116" t="n">
-        <v>7204056</v>
+        <v>7203982</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13560,7 +13542,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13570,7 +13552,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13597,7 +13579,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119536907</v>
+        <v>119536872</v>
       </c>
       <c r="B117" t="n">
         <v>78526</v>
@@ -13637,10 +13619,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>539291</v>
+        <v>539509</v>
       </c>
       <c r="R117" t="n">
-        <v>7204060</v>
+        <v>7203558</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13672,7 +13654,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13682,7 +13664,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13709,7 +13691,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119536891</v>
+        <v>119536871</v>
       </c>
       <c r="B118" t="n">
         <v>78526</v>
@@ -13749,10 +13731,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>539381</v>
+        <v>539512</v>
       </c>
       <c r="R118" t="n">
-        <v>7203929</v>
+        <v>7203548</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13784,7 +13766,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13794,7 +13776,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13821,10 +13803,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119536895</v>
+        <v>119536107</v>
       </c>
       <c r="B119" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13837,34 +13819,43 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>539355</v>
+        <v>539353</v>
       </c>
       <c r="R119" t="n">
-        <v>7203976</v>
+        <v>7203941</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13896,7 +13887,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13906,7 +13897,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13933,10 +13924,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119536007</v>
+        <v>119537112</v>
       </c>
       <c r="B120" t="n">
-        <v>90562</v>
+        <v>91128</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13945,25 +13936,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13973,10 +13964,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>539248</v>
+        <v>539486</v>
       </c>
       <c r="R120" t="n">
-        <v>7203984</v>
+        <v>7203594</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -14008,7 +13999,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14018,7 +14009,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14045,10 +14036,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119536001</v>
+        <v>119536331</v>
       </c>
       <c r="B121" t="n">
-        <v>90562</v>
+        <v>79608</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14061,21 +14052,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14085,10 +14076,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>539342</v>
+        <v>539389</v>
       </c>
       <c r="R121" t="n">
-        <v>7204082</v>
+        <v>7203819</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -14120,7 +14111,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14130,7 +14121,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14157,10 +14148,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119536765</v>
+        <v>119536896</v>
       </c>
       <c r="B122" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14173,21 +14164,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14197,10 +14188,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>539440</v>
+        <v>539337</v>
       </c>
       <c r="R122" t="n">
-        <v>7203703</v>
+        <v>7203986</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14232,7 +14223,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14242,7 +14233,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14269,7 +14260,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119536908</v>
+        <v>119536901</v>
       </c>
       <c r="B123" t="n">
         <v>78526</v>
@@ -14309,10 +14300,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>539246</v>
+        <v>539322</v>
       </c>
       <c r="R123" t="n">
-        <v>7203987</v>
+        <v>7204109</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14344,7 +14335,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14354,7 +14345,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14381,10 +14372,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119536888</v>
+        <v>119536520</v>
       </c>
       <c r="B124" t="n">
-        <v>78526</v>
+        <v>96862</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14393,25 +14384,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14421,10 +14412,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>539404</v>
+        <v>539260</v>
       </c>
       <c r="R124" t="n">
-        <v>7203854</v>
+        <v>7203982</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -14456,7 +14447,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14466,7 +14457,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14493,10 +14484,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119536876</v>
+        <v>119536682</v>
       </c>
       <c r="B125" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14505,25 +14496,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14533,10 +14524,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>539520</v>
+        <v>539270</v>
       </c>
       <c r="R125" t="n">
-        <v>7203615</v>
+        <v>7204025</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14568,7 +14559,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14578,7 +14569,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14605,10 +14596,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119536754</v>
+        <v>119536096</v>
       </c>
       <c r="B126" t="n">
-        <v>56514</v>
+        <v>56522</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14617,35 +14608,30 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14654,10 +14640,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>539402</v>
+        <v>539506</v>
       </c>
       <c r="R126" t="n">
-        <v>7203785</v>
+        <v>7203636</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14689,7 +14675,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14699,12 +14685,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>17:02</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Familjegrupp</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14731,10 +14712,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119537245</v>
+        <v>119536765</v>
       </c>
       <c r="B127" t="n">
-        <v>90957</v>
+        <v>90558</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14743,25 +14724,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4217</v>
+        <v>1108</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14771,10 +14752,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>539319</v>
+        <v>539440</v>
       </c>
       <c r="R127" t="n">
-        <v>7204161</v>
+        <v>7203703</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14806,7 +14787,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14816,7 +14797,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14843,10 +14824,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119536915</v>
+        <v>119536483</v>
       </c>
       <c r="B128" t="n">
-        <v>78526</v>
+        <v>91005</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14855,25 +14836,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14883,10 +14864,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>539474</v>
+        <v>539427</v>
       </c>
       <c r="R128" t="n">
-        <v>7203605</v>
+        <v>7203755</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14918,7 +14899,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14928,7 +14909,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14955,7 +14936,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119536333</v>
+        <v>119536335</v>
       </c>
       <c r="B129" t="n">
         <v>79608</v>
@@ -14995,10 +14976,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>539410</v>
+        <v>539371</v>
       </c>
       <c r="R129" t="n">
-        <v>7203877</v>
+        <v>7203932</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -15030,7 +15011,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15040,7 +15021,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15067,7 +15048,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119536338</v>
+        <v>119536340</v>
       </c>
       <c r="B130" t="n">
         <v>79608</v>
@@ -15107,10 +15088,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>539333</v>
+        <v>539325</v>
       </c>
       <c r="R130" t="n">
-        <v>7204016</v>
+        <v>7204093</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -15142,7 +15123,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15152,7 +15133,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15179,10 +15160,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119536346</v>
+        <v>119536403</v>
       </c>
       <c r="B131" t="n">
-        <v>79608</v>
+        <v>94323</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15191,25 +15172,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2081</v>
+        <v>2813</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15219,10 +15200,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>539419</v>
+        <v>539514</v>
       </c>
       <c r="R131" t="n">
-        <v>7203720</v>
+        <v>7203744</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -15254,7 +15235,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15264,7 +15245,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15291,10 +15272,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119536336</v>
+        <v>119536899</v>
       </c>
       <c r="B132" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15307,21 +15288,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15331,10 +15312,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>539352</v>
+        <v>539342</v>
       </c>
       <c r="R132" t="n">
-        <v>7203941</v>
+        <v>7204082</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -15366,7 +15347,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15376,7 +15357,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15403,7 +15384,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119536911</v>
+        <v>119536875</v>
       </c>
       <c r="B133" t="n">
         <v>78526</v>
@@ -15443,10 +15424,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>539314</v>
+        <v>539503</v>
       </c>
       <c r="R133" t="n">
-        <v>7203905</v>
+        <v>7203619</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -15478,7 +15459,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15488,7 +15469,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15515,10 +15496,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119536914</v>
+        <v>119536707</v>
       </c>
       <c r="B134" t="n">
-        <v>78526</v>
+        <v>57421</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15527,38 +15508,47 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>539438</v>
+        <v>539474</v>
       </c>
       <c r="R134" t="n">
-        <v>7203711</v>
+        <v>7203674</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -15590,7 +15580,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15600,7 +15590,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15627,10 +15617,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119536905</v>
+        <v>119535949</v>
       </c>
       <c r="B135" t="n">
-        <v>78526</v>
+        <v>104994</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15639,25 +15629,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15667,10 +15657,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>539319</v>
+        <v>539400</v>
       </c>
       <c r="R135" t="n">
-        <v>7204163</v>
+        <v>7203837</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -15702,7 +15692,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15712,7 +15702,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15739,10 +15729,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119536685</v>
+        <v>119536348</v>
       </c>
       <c r="B136" t="n">
-        <v>79643</v>
+        <v>79608</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15751,25 +15741,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15779,10 +15769,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>539419</v>
+        <v>539466</v>
       </c>
       <c r="R136" t="n">
-        <v>7203720</v>
+        <v>7203618</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15814,7 +15804,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15824,7 +15814,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15851,10 +15841,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119536684</v>
+        <v>119536333</v>
       </c>
       <c r="B137" t="n">
-        <v>79643</v>
+        <v>79608</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15863,25 +15853,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15891,10 +15881,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>539409</v>
+        <v>539410</v>
       </c>
       <c r="R137" t="n">
-        <v>7203733</v>
+        <v>7203877</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -15926,7 +15916,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15936,7 +15926,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15963,10 +15953,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119536872</v>
+        <v>119536276</v>
       </c>
       <c r="B138" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15975,25 +15965,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -16003,10 +15993,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>539509</v>
+        <v>539490</v>
       </c>
       <c r="R138" t="n">
-        <v>7203558</v>
+        <v>7203595</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -16038,7 +16028,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16048,7 +16038,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16075,7 +16065,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119536894</v>
+        <v>119536897</v>
       </c>
       <c r="B139" t="n">
         <v>78526</v>
@@ -16115,10 +16105,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>539344</v>
+        <v>539335</v>
       </c>
       <c r="R139" t="n">
-        <v>7203950</v>
+        <v>7204015</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -16150,7 +16140,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16160,7 +16150,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16187,7 +16177,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119536903</v>
+        <v>119536883</v>
       </c>
       <c r="B140" t="n">
         <v>78526</v>
@@ -16227,10 +16217,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>539306</v>
+        <v>539438</v>
       </c>
       <c r="R140" t="n">
-        <v>7204148</v>
+        <v>7203740</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -16262,7 +16252,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16272,7 +16262,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16299,10 +16289,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119536716</v>
+        <v>119536273</v>
       </c>
       <c r="B141" t="n">
-        <v>80483</v>
+        <v>79636</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16311,25 +16301,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1049</v>
+        <v>6462</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16339,10 +16329,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>539315</v>
+        <v>539392</v>
       </c>
       <c r="R141" t="n">
-        <v>7203955</v>
+        <v>7203821</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -16374,7 +16364,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16384,7 +16374,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16411,10 +16401,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119536331</v>
+        <v>119536895</v>
       </c>
       <c r="B142" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16427,21 +16417,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16451,10 +16441,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>539389</v>
+        <v>539355</v>
       </c>
       <c r="R142" t="n">
-        <v>7203819</v>
+        <v>7203976</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -16486,7 +16476,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16496,7 +16486,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16523,10 +16513,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119536334</v>
+        <v>119536270</v>
       </c>
       <c r="B143" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16535,25 +16525,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16563,10 +16553,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>539383</v>
+        <v>539441</v>
       </c>
       <c r="R143" t="n">
-        <v>7203898</v>
+        <v>7203738</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -16598,7 +16588,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16608,7 +16598,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16635,7 +16625,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119536913</v>
+        <v>119536888</v>
       </c>
       <c r="B144" t="n">
         <v>78526</v>
@@ -16675,10 +16665,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>539418</v>
+        <v>539404</v>
       </c>
       <c r="R144" t="n">
-        <v>7203718</v>
+        <v>7203854</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -16710,7 +16700,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16720,7 +16710,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16747,10 +16737,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119537248</v>
+        <v>119536020</v>
       </c>
       <c r="B145" t="n">
-        <v>77910</v>
+        <v>57310</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16763,34 +16753,39 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>539311</v>
+        <v>539508</v>
       </c>
       <c r="R145" t="n">
-        <v>7203961</v>
+        <v>7203619</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -16822,7 +16817,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16832,7 +16827,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16859,10 +16854,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119536680</v>
+        <v>119536027</v>
       </c>
       <c r="B146" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16871,38 +16866,43 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>539505</v>
+        <v>539326</v>
       </c>
       <c r="R146" t="n">
-        <v>7203636</v>
+        <v>7204100</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16944,7 +16944,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD146" t="b">
